--- a/coin.xlsx
+++ b/coin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luoxi/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luoxi/Desktop/map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DD625F-8749-A34F-B7C4-6619EC7D6F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB9E8D7-4EE5-EB4C-9CC5-2AE6AB155C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="760" windowWidth="28100" windowHeight="17120" xr2:uid="{C48DE3EE-EDDE-F745-9FF9-B245AC008524}"/>
+    <workbookView xWindow="12820" yWindow="700" windowWidth="25600" windowHeight="14860" xr2:uid="{C48DE3EE-EDDE-F745-9FF9-B245AC008524}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3793" uniqueCount="2413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4275" uniqueCount="2888">
   <si>
     <t>ID</t>
   </si>
@@ -7358,6 +7358,1432 @@
   <si>
     <t>Attribute Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kingdom of Lydia (1300–546 BCE)</t>
+  </si>
+  <si>
+    <t>Kingdom of Lydia (1300–547 BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–1st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–2st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–3st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–4st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–5st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–6st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–7st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–8st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–9st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–10st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–11st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–12st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–13st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–14st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–15st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–16st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–17st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–18st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–19st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–20st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–21st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–22st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–23st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–24st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–25st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–26st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–27st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–28st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–29st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–30st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–31st century BCE)</t>
+  </si>
+  <si>
+    <t>Ancient Greece and the Mediterranean Coast (510 BCE–32st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–1st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–2st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–3st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–4st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–5st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–6st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–7st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–8st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–9st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–10st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–11st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–12st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–13st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–14st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–15st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–16st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–17st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–18st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–19st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–20st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–21st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–22st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–23st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–24st century BCE)</t>
+  </si>
+  <si>
+    <t>Empire of Alexander the Great and Hellenistic Era (335 BCE–25st century BCE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–476 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–477 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–478 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–479 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–480 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–481 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–482 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–483 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–484 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–485 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–486 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–487 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–488 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–489 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–490 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–491 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–492 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–493 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–494 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–495 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–496 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–497 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–498 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–499 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–500 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–501 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–502 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–503 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–504 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–505 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–506 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–507 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–508 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–509 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–510 CE)</t>
+  </si>
+  <si>
+    <t>Roman Empire (289 BCE–511 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1453 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1454 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1455 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1456 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1457 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1458 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1459 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1460 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1461 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1462 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1463 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1464 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1465 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1466 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1467 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1468 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1469 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1470 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1471 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1472 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1473 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1474 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1475 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1476 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1477 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1478 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1479 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1480 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1481 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1482 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1483 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1484 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1485 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1486 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1487 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1488 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1489 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1490 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1491 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1492 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1493 CE)</t>
+  </si>
+  <si>
+    <t>Byzantine Empire (395–1494 CE)</t>
+  </si>
+  <si>
+    <t>Achaemenid Empire (550–330 BCE)</t>
+  </si>
+  <si>
+    <t>Achaemenid Empire (550–331 BCE)</t>
+  </si>
+  <si>
+    <t>Achaemenid Empire (550–332 BCE)</t>
+  </si>
+  <si>
+    <t>Achaemenid Empire (550–333 BCE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–224 CE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–225 CE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–226 CE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–227 CE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–228 CE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–229 CE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–230 CE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–231 CE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–232 CE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–233 CE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–234 CE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–235 CE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–236 CE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–237 CE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–238 CE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–239 CE)</t>
+  </si>
+  <si>
+    <t>Parthian Empire (247 BCE–240 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–642 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–643 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–644 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–645 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–646 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–647 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–648 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–649 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–650 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–651 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–652 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–653 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–654 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–655 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–656 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–657 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–658 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–659 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–660 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–661 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–662 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–663 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–664 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–665 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–666 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–667 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–668 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–669 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–670 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–671 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–672 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–673 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–674 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–675 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–676 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–677 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–678 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–679 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–680 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–681 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–682 CE)</t>
+  </si>
+  <si>
+    <t>Sassanian Empire (226–683 CE)</t>
+  </si>
+  <si>
+    <t>Bactrian-Greek and Indo-Greek Kingdom (250 BCE–1st century BCE)</t>
+  </si>
+  <si>
+    <t>Bactrian-Greek and Indo-Greek Kingdom (250 BCE–2st century BCE)</t>
+  </si>
+  <si>
+    <t>Bactrian-Greek and Indo-Greek Kingdom (250 BCE–3st century BCE)</t>
+  </si>
+  <si>
+    <t>Bactrian-Greek and Indo-Greek Kingdom (250 BCE–4st century BCE)</t>
+  </si>
+  <si>
+    <t>Bactrian-Greek and Indo-Greek Kingdom (250 BCE–5st century BCE)</t>
+  </si>
+  <si>
+    <t>Bactrian-Greek and Indo-Greek Kingdom (250 BCE–6st century BCE)</t>
+  </si>
+  <si>
+    <t>Bactrian-Greek and Indo-Greek Kingdom (250 BCE–7st century BCE)</t>
+  </si>
+  <si>
+    <t>Bactrian-Greek and Indo-Greek Kingdom (250 BCE–8st century BCE)</t>
+  </si>
+  <si>
+    <t>Bactrian-Greek and Indo-Greek Kingdom (250 BCE–9st century BCE)</t>
+  </si>
+  <si>
+    <t>Indo-Scythian Kingdom (90 BCE–10 CE)</t>
+  </si>
+  <si>
+    <t>Indo-Scythian Kingdom (90 BCE–11 CE)</t>
+  </si>
+  <si>
+    <t>Indo-Scythian Kingdom (90 BCE–12 CE)</t>
+  </si>
+  <si>
+    <t>Indo-Scythian Kingdom (90 BCE–13 CE)</t>
+  </si>
+  <si>
+    <t>Indo-Scythian Kingdom (90 BCE–14 CE)</t>
+  </si>
+  <si>
+    <t>Western Satraps (35–405 CE)</t>
+  </si>
+  <si>
+    <t>Western Satraps (35–406 CE)</t>
+  </si>
+  <si>
+    <t>Western Satraps (35–407 CE)</t>
+  </si>
+  <si>
+    <t>Western Satraps (35–408 CE)</t>
+  </si>
+  <si>
+    <t>Western Satraps (35–409 CE)</t>
+  </si>
+  <si>
+    <t>Maitraka Dynasty (470–780 CE)</t>
+  </si>
+  <si>
+    <t>Maitraka Dynasty (470–781 CE)</t>
+  </si>
+  <si>
+    <t>Indo-Parthian Kingdom (20–240 CE)</t>
+  </si>
+  <si>
+    <t>Indo-Parthian Kingdom (20–241 CE)</t>
+  </si>
+  <si>
+    <t>Indo-Parthian Kingdom (20–242 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–425 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–426 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–427 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–428 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–429 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–430 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–431 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–432 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–433 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–434 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–435 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–436 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–437 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–438 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–439 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–440 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–441 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–442 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–443 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–444 CE)</t>
+  </si>
+  <si>
+    <t>Kushan Empire (55–445 CE)</t>
+  </si>
+  <si>
+    <t>Kushano-Sassanian Kingdom (230–977 CE)</t>
+  </si>
+  <si>
+    <t>Kushano-Sassanian Kingdom (230–978 CE)</t>
+  </si>
+  <si>
+    <t>Kushano-Sassanian Kingdom (230–979 CE)</t>
+  </si>
+  <si>
+    <t>Kushano-Sassanian Kingdom (230–980 CE)</t>
+  </si>
+  <si>
+    <t>Kushano-Sassanian Kingdom (230–981 CE)</t>
+  </si>
+  <si>
+    <t>Kushano-Sassanian Kingdom (230–982 CE)</t>
+  </si>
+  <si>
+    <t>Kidarite Kingdom (360–5th century CE)</t>
+  </si>
+  <si>
+    <t>Kidarite Kingdom (360–6th century CE)</t>
+  </si>
+  <si>
+    <t>Kidarite Kingdom (360–7th century CE)</t>
+  </si>
+  <si>
+    <t>Kidarite Kingdom (360–8th century CE)</t>
+  </si>
+  <si>
+    <t>Kidarite Kingdom (360–9th century CE)</t>
+  </si>
+  <si>
+    <t>Kidarite Kingdom (360–10th century CE)</t>
+  </si>
+  <si>
+    <t>Kidarite Kingdom (360–11th century CE)</t>
+  </si>
+  <si>
+    <t>Kidarite Kingdom (360–12th century CE)</t>
+  </si>
+  <si>
+    <t>Northern Tokharian (5th–7th century CE)</t>
+  </si>
+  <si>
+    <t>Northern Tokharian (5th–8th century CE)</t>
+  </si>
+  <si>
+    <t>Khwarazmian Dynasty (4th–8th century CE)</t>
+  </si>
+  <si>
+    <t>Sogdian Kingdom (4th–7th century CE)</t>
+  </si>
+  <si>
+    <t>Sogdian Kingdom (4th–8th century CE)</t>
+  </si>
+  <si>
+    <t>Gandhara (6th century BCE)</t>
+  </si>
+  <si>
+    <t>Hephthalite Empire (4th–6th century CE)</t>
+  </si>
+  <si>
+    <t>Hephthalite Empire (4th–7th century CE)</t>
+  </si>
+  <si>
+    <t>Hephthalite Empire (4th–8th century CE)</t>
+  </si>
+  <si>
+    <t>Hephthalite Empire (4th–9th century CE)</t>
+  </si>
+  <si>
+    <t>Western Turkic Khaganate (560–610 CE)</t>
+  </si>
+  <si>
+    <t>Western Turkic Khaganate (560–611 CE)</t>
+  </si>
+  <si>
+    <t>Western Turkic Khaganate (560–612 CE)</t>
+  </si>
+  <si>
+    <t>Gandhara (7th century BCE)</t>
+  </si>
+  <si>
+    <t>Gandhara (8th century BCE)</t>
+  </si>
+  <si>
+    <t>Maurya Empire (324–185 BCE)</t>
+  </si>
+  <si>
+    <t>Maurya Empire (324–186 BCE)</t>
+  </si>
+  <si>
+    <t>Maurya Empire (324–187 BCE)</t>
+  </si>
+  <si>
+    <t>Maurya Empire (324–188 BCE)</t>
+  </si>
+  <si>
+    <t>Maurya Empire (324–189 BCE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–540 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–541 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–542 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–543 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–544 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–545 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–546 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–547 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–548 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–549 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–550 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–551 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–552 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–553 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–554 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–555 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–556 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–557 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–558 CE)</t>
+  </si>
+  <si>
+    <t>Gupta Empire (320–559 CE)</t>
+  </si>
+  <si>
+    <t>Yadava Dynasty (1100–1313 CE)</t>
+  </si>
+  <si>
+    <t>Yadava Dynasty (1100–1314 CE)</t>
+  </si>
+  <si>
+    <t>Yadava Dynasty (1100–1315 CE)</t>
+  </si>
+  <si>
+    <t>Yadava Dynasty (1100–1316 CE)</t>
+  </si>
+  <si>
+    <t>Yadava Dynasty (1100–1317 CE)</t>
+  </si>
+  <si>
+    <t>Vijayanagara Empire (1336–1670 CE)</t>
+  </si>
+  <si>
+    <t>Vijayanagara Empire (1336–1671 CE)</t>
+  </si>
+  <si>
+    <t>Ahom Kingdom (13th century–1824 CE)</t>
+  </si>
+  <si>
+    <t>Ahom Kingdom (13th century–1825 CE)</t>
+  </si>
+  <si>
+    <t>Umayyad Caliphate (661–750 CE)</t>
+  </si>
+  <si>
+    <t>Umayyad Caliphate (661–751 CE)</t>
+  </si>
+  <si>
+    <t>Umayyad Caliphate (661–752 CE)</t>
+  </si>
+  <si>
+    <t>Umayyad Caliphate (661–753 CE)</t>
+  </si>
+  <si>
+    <t>Umayyad Caliphate (661–754 CE)</t>
+  </si>
+  <si>
+    <t>Umayyad Caliphate (661–755 CE)</t>
+  </si>
+  <si>
+    <t>Umayyad Caliphate (661–756 CE)</t>
+  </si>
+  <si>
+    <t>Abbasid Caliphate (750–1258 CE)</t>
+  </si>
+  <si>
+    <t>Abbasid Caliphate (750–1259 CE)</t>
+  </si>
+  <si>
+    <t>Abbasid Caliphate (750–1260 CE)</t>
+  </si>
+  <si>
+    <t>Abbasid Caliphate (750–1261 CE)</t>
+  </si>
+  <si>
+    <t>Abbasid Caliphate (750–1262 CE)</t>
+  </si>
+  <si>
+    <t>Abbasid Caliphate (750–1263 CE)</t>
+  </si>
+  <si>
+    <t>Abbasid Caliphate (750–1264 CE)</t>
+  </si>
+  <si>
+    <t>Abbasid Caliphate (750–1265 CE)</t>
+  </si>
+  <si>
+    <t>Abbasid Caliphate (750–1266 CE)</t>
+  </si>
+  <si>
+    <t>Tulunid Dynasty (868–905 CE)</t>
+  </si>
+  <si>
+    <t>Tulunid Dynasty (868–906 CE)</t>
+  </si>
+  <si>
+    <t>Fatimid Caliphate (909–1171 CE)</t>
+  </si>
+  <si>
+    <t>Fatimid Caliphate (909–1172 CE)</t>
+  </si>
+  <si>
+    <t>Fatimid Caliphate (909–1173 CE)</t>
+  </si>
+  <si>
+    <t>Fatimid Caliphate (909–1174 CE)</t>
+  </si>
+  <si>
+    <t>Fatimid Caliphate (909–1175 CE)</t>
+  </si>
+  <si>
+    <t>Fatimid Caliphate (909–1176 CE)</t>
+  </si>
+  <si>
+    <t>Ayyubid Dynasty (12th–13th century CE)</t>
+  </si>
+  <si>
+    <t>Ayyubid Dynasty (12th–14th century CE)</t>
+  </si>
+  <si>
+    <t>Ayyubid Dynasty (12th–15th century CE)</t>
+  </si>
+  <si>
+    <t>Ayyubid Dynasty (12th–16th century CE)</t>
+  </si>
+  <si>
+    <t>Mamluk Sultanate (1250–1517 CE)</t>
+  </si>
+  <si>
+    <t>Mamluk Sultanate (1250–1518 CE)</t>
+  </si>
+  <si>
+    <t>Sultanate of Rum (1077–1308 CE)</t>
+  </si>
+  <si>
+    <t>Sultanate of Rum (1077–1309 CE)</t>
+  </si>
+  <si>
+    <t>Sultanate of Rum (1077–1310 CE)</t>
+  </si>
+  <si>
+    <t>Hafsid Dynasty (13th–16th century CE)</t>
+  </si>
+  <si>
+    <t>Ottoman Empire (1299–1923 CE)</t>
+  </si>
+  <si>
+    <t>Ottoman Empire (1299–1924 CE)</t>
+  </si>
+  <si>
+    <t>Ottoman Empire (1299–1925 CE)</t>
+  </si>
+  <si>
+    <t>Tahirid Dynasty (820–872 CE)</t>
+  </si>
+  <si>
+    <t>Samanid Dynasty (9th–10th century CE)</t>
+  </si>
+  <si>
+    <t>Samanid Dynasty (9th–11th century CE)</t>
+  </si>
+  <si>
+    <t>Samanid Dynasty (9th–12th century CE)</t>
+  </si>
+  <si>
+    <t>Samanid Dynasty (9th–13th century CE)</t>
+  </si>
+  <si>
+    <t>Samanid Dynasty (9th–14th century CE)</t>
+  </si>
+  <si>
+    <t>Samanid Dynasty (9th–15th century CE)</t>
+  </si>
+  <si>
+    <t>Samanid Dynasty (9th–16th century CE)</t>
+  </si>
+  <si>
+    <t>Buyid Dynasty (932–1055 CE)</t>
+  </si>
+  <si>
+    <t>Buyid Dynasty (932–1056 CE)</t>
+  </si>
+  <si>
+    <t>Ghaznavid Dynasty (962–1186 CE)</t>
+  </si>
+  <si>
+    <t>Ghaznavid Dynasty (962–1187 CE)</t>
+  </si>
+  <si>
+    <t>Ghaznavid Dynasty (962–1188 CE)</t>
+  </si>
+  <si>
+    <t>Ghaznavid Dynasty (962–1189 CE)</t>
+  </si>
+  <si>
+    <t>Ghaznavid Dynasty (962–1190 CE)</t>
+  </si>
+  <si>
+    <t>Ghaznavid Dynasty (962–1191 CE)</t>
+  </si>
+  <si>
+    <t>Seljuk Empire (1037–1194 CE)</t>
+  </si>
+  <si>
+    <t>Seljuk Empire (1037–1195 CE)</t>
+  </si>
+  <si>
+    <t>Seljuk Empire (1037–1196 CE)</t>
+  </si>
+  <si>
+    <t>Khwarazmian Empire (700–1231 CE)</t>
+  </si>
+  <si>
+    <t>Khwarazmian Empire (700–1232 CE)</t>
+  </si>
+  <si>
+    <t>Khwarazmian Empire (700–1233 CE)</t>
+  </si>
+  <si>
+    <t>Khwarazmian Empire (700–1234 CE)</t>
+  </si>
+  <si>
+    <t>Ghurid Dynasty (1148–1215 CE)</t>
+  </si>
+  <si>
+    <t>Ghurid Dynasty (1148–1216 CE)</t>
+  </si>
+  <si>
+    <t>Ghurid Dynasty (1148–1217 CE)</t>
+  </si>
+  <si>
+    <t>Ghurid Dynasty (1148–1218 CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–17th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–18th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–19th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–20th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–21th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–22th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–23th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–24th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–25th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–26th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–27th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–28th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–29th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–30th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–31th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–32th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–33th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–34th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–35th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–36th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–37th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–38th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–39th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–40th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–41th century CE)</t>
+  </si>
+  <si>
+    <t>Mongol Empire (1206–42th century CE)</t>
+  </si>
+  <si>
+    <t>Timurid Empire (1370–1507 CE)</t>
+  </si>
+  <si>
+    <t>Safavid Dynasty (1501–1736 CE)</t>
+  </si>
+  <si>
+    <t>Safavid Dynasty (1501–1737 CE)</t>
+  </si>
+  <si>
+    <t>Safavid Dynasty (1501–1738 CE)</t>
+  </si>
+  <si>
+    <t>Safavid Dynasty (1501–1739 CE)</t>
+  </si>
+  <si>
+    <t>Safavid Dynasty (1501–1740 CE)</t>
+  </si>
+  <si>
+    <t>Safavid Dynasty (1501–1741 CE)</t>
+  </si>
+  <si>
+    <t>Afsharid Dynasty (1735–1796 CE)</t>
+  </si>
+  <si>
+    <t>Afsharid Dynasty (1735–1797 CE)</t>
+  </si>
+  <si>
+    <t>Afsharid Dynasty (1735–1798 CE)</t>
+  </si>
+  <si>
+    <t>Afsharid Dynasty (1735–1799 CE)</t>
+  </si>
+  <si>
+    <t>Afsharid Dynasty (1735–1800 CE)</t>
+  </si>
+  <si>
+    <t>Zand Dynasty (18th century CE)</t>
+  </si>
+  <si>
+    <t>Zand Dynasty (19th century CE)</t>
+  </si>
+  <si>
+    <t>Qajar Dynasty (1779–1921 CE)</t>
+  </si>
+  <si>
+    <t>Qajar Dynasty (1779–1922 CE)</t>
+  </si>
+  <si>
+    <t>Qajar Dynasty (1779–1923 CE)</t>
+  </si>
+  <si>
+    <t>Qajar Dynasty (1779–1924 CE)</t>
+  </si>
+  <si>
+    <t>Qajar Dynasty (1779–1925 CE)</t>
+  </si>
+  <si>
+    <t>Shaybanid Dynasty (1500–1598 CE)</t>
+  </si>
+  <si>
+    <t>Shaybanid Dynasty (1500–1599 CE)</t>
+  </si>
+  <si>
+    <t>Shaybanid Dynasty (1500–1601 CE)</t>
+  </si>
+  <si>
+    <t>Shaybanid Dynasty (1500–1600 CE)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sindh Princely States (9th–11th century CE)</t>
+  </si>
+  <si>
+    <t>Sindh Princely States (9th–12th century CE)</t>
+  </si>
+  <si>
+    <t>Sindh Princely States (9th–13th century CE)</t>
+  </si>
+  <si>
+    <t>Mamluk Sultanate (Delhi) (1206–1290 CE)</t>
+  </si>
+  <si>
+    <t>Mamluk Sultanate (Delhi) (1206–1291 CE)</t>
+  </si>
+  <si>
+    <t>Mamluk Sultanate (Delhi) (1206–1292 CE)</t>
+  </si>
+  <si>
+    <t>Khalji Dynasty (1290–1320 CE)</t>
+  </si>
+  <si>
+    <t>Khalji Dynasty (1290–1321 CE)</t>
+  </si>
+  <si>
+    <t>Khalji Dynasty (1290–1322 CE)</t>
+  </si>
+  <si>
+    <t>Khalji Dynasty (1290–1323 CE)</t>
+  </si>
+  <si>
+    <t>Tughlaq Dynasty (1320–1413 CE)</t>
+  </si>
+  <si>
+    <t>Tughlaq Dynasty (1320–1414 CE)</t>
+  </si>
+  <si>
+    <t>Tughlaq Dynasty (1320–1415 CE)</t>
+  </si>
+  <si>
+    <t>Sur Empire (1539–1557 CE)</t>
+  </si>
+  <si>
+    <t>Sur Empire (1539–1558 CE)</t>
+  </si>
+  <si>
+    <t>Bahmanid Sultanate (1347–1518 CE)</t>
+  </si>
+  <si>
+    <t>Malwa Sultanate (1401–1562 CE)</t>
+  </si>
+  <si>
+    <t>Malwa Sultanate (1401–1563 CE)</t>
+  </si>
+  <si>
+    <t>Malwa Sultanate (1401–1564 CE)</t>
+  </si>
+  <si>
+    <t>Gujarat Sultanate (1297–1576 CE)</t>
+  </si>
+  <si>
+    <t>Gujarat Sultanate (1297–1577 CE)</t>
+  </si>
+  <si>
+    <t>Bengal Sultanate (1338–1576 CE)</t>
+  </si>
+  <si>
+    <t>Bengal Sultanate (1338–1577 CE)</t>
+  </si>
+  <si>
+    <t>Bengal Sultanate (1338–1578 CE)</t>
+  </si>
+  <si>
+    <t>Jaunpur Sultanate (1359–1479 CE)</t>
+  </si>
+  <si>
+    <t>Mughal Empire (1526–1857 CE)</t>
+  </si>
+  <si>
+    <t>Mughal Empire (1526–1858 CE)</t>
+  </si>
+  <si>
+    <t>Mughal Empire (1526–1859 CE)</t>
+  </si>
+  <si>
+    <t>Mughal Empire (1526–1860 CE)</t>
+  </si>
+  <si>
+    <t>Mughal Empire (1526–1861 CE)</t>
+  </si>
+  <si>
+    <t>Mughal Empire (1526–1862 CE)</t>
+  </si>
+  <si>
+    <t>Mughal Empire (1526–1863 CE)</t>
+  </si>
+  <si>
+    <t>Mughal Empire (1526–1864 CE)</t>
+  </si>
+  <si>
+    <t>Mughal Empire (1526–1865 CE)</t>
+  </si>
+  <si>
+    <t>Mughal Empire (1526–1866 CE)</t>
+  </si>
+  <si>
+    <t>Mughal Empire (1526–1867 CE)</t>
+  </si>
+  <si>
+    <t>Mughal Empire (1526–1868 CE)</t>
+  </si>
+  <si>
+    <t>Mughal Empire (1526–1869 CE)</t>
+  </si>
+  <si>
+    <t>Mughal Empire (1526–1870 CE)</t>
+  </si>
+  <si>
+    <t>Mughal Empire (1526–1871 CE)</t>
+  </si>
+  <si>
+    <t>Mughal Empire (1526–1872 CE)</t>
+  </si>
+  <si>
+    <t>Sikh Empire (1707–1849 CE)</t>
+  </si>
+  <si>
+    <t>Durrani Empire (1747–1818 CE)</t>
+  </si>
+  <si>
+    <t>Barakzai Dynasty (1818–1973 CE)</t>
+  </si>
+  <si>
+    <t>Durrani Empire (1747–1819 CE)</t>
+  </si>
+  <si>
+    <t>Durrani Empire (1747–1820 CE)</t>
+  </si>
+  <si>
+    <t>Durrani Empire (1747–1821 CE)</t>
+  </si>
+  <si>
+    <t>Durrani Empire (1747–1822 CE)</t>
+  </si>
+  <si>
+    <t>Durrani Empire (1747–1823 CE)</t>
+  </si>
+  <si>
+    <t>Barakzai Dynasty (1818–1974 CE)</t>
+  </si>
+  <si>
+    <t>Barakzai Dynasty (1818–1975 CE)</t>
+  </si>
+  <si>
+    <t>Barakzai Dynasty (1818–1976 CE)</t>
+  </si>
+  <si>
+    <t>Bukhara Khanate (1785–1920 CE)</t>
+  </si>
+  <si>
+    <t>Khokand Khanate (1865–1876 CE)</t>
   </si>
 </sst>
 </file>
@@ -7813,6 +9239,9 @@
       <c r="B2" s="1">
         <v>1</v>
       </c>
+      <c r="C2" t="s">
+        <v>2413</v>
+      </c>
       <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
@@ -7848,6 +9277,9 @@
       <c r="B3" s="1">
         <v>1</v>
       </c>
+      <c r="C3" t="s">
+        <v>2414</v>
+      </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
@@ -7883,6 +9315,9 @@
       <c r="B4" s="1">
         <v>2</v>
       </c>
+      <c r="C4" t="s">
+        <v>2415</v>
+      </c>
       <c r="D4" s="1" t="s">
         <v>26</v>
       </c>
@@ -7918,6 +9353,9 @@
       <c r="B5" s="1">
         <v>2</v>
       </c>
+      <c r="C5" t="s">
+        <v>2416</v>
+      </c>
       <c r="D5" s="1" t="s">
         <v>33</v>
       </c>
@@ -7953,6 +9391,9 @@
       <c r="B6" s="1">
         <v>2</v>
       </c>
+      <c r="C6" t="s">
+        <v>2417</v>
+      </c>
       <c r="D6" s="1" t="s">
         <v>40</v>
       </c>
@@ -7988,6 +9429,9 @@
       <c r="B7" s="1">
         <v>2</v>
       </c>
+      <c r="C7" t="s">
+        <v>2418</v>
+      </c>
       <c r="D7" s="1" t="s">
         <v>49</v>
       </c>
@@ -8023,6 +9467,9 @@
       <c r="B8" s="1">
         <v>2</v>
       </c>
+      <c r="C8" t="s">
+        <v>2419</v>
+      </c>
       <c r="D8" s="1" t="s">
         <v>54</v>
       </c>
@@ -8058,6 +9505,9 @@
       <c r="B9" s="1">
         <v>2</v>
       </c>
+      <c r="C9" t="s">
+        <v>2420</v>
+      </c>
       <c r="D9" s="1" t="s">
         <v>65</v>
       </c>
@@ -8093,6 +9543,9 @@
       <c r="B10" s="1">
         <v>2</v>
       </c>
+      <c r="C10" t="s">
+        <v>2421</v>
+      </c>
       <c r="D10" s="1" t="s">
         <v>71</v>
       </c>
@@ -8128,6 +9581,9 @@
       <c r="B11" s="1">
         <v>2</v>
       </c>
+      <c r="C11" t="s">
+        <v>2422</v>
+      </c>
       <c r="D11" s="1" t="s">
         <v>75</v>
       </c>
@@ -8163,6 +9619,9 @@
       <c r="B12" s="1">
         <v>2</v>
       </c>
+      <c r="C12" t="s">
+        <v>2423</v>
+      </c>
       <c r="D12" s="1" t="s">
         <v>79</v>
       </c>
@@ -8198,6 +9657,9 @@
       <c r="B13" s="1">
         <v>2</v>
       </c>
+      <c r="C13" t="s">
+        <v>2424</v>
+      </c>
       <c r="D13" s="1" t="s">
         <v>88</v>
       </c>
@@ -8233,6 +9695,9 @@
       <c r="B14" s="1">
         <v>2</v>
       </c>
+      <c r="C14" t="s">
+        <v>2425</v>
+      </c>
       <c r="D14" s="1" t="s">
         <v>96</v>
       </c>
@@ -8268,6 +9733,9 @@
       <c r="B15" s="1">
         <v>2</v>
       </c>
+      <c r="C15" t="s">
+        <v>2426</v>
+      </c>
       <c r="D15" s="1" t="s">
         <v>105</v>
       </c>
@@ -8303,6 +9771,9 @@
       <c r="B16" s="1">
         <v>2</v>
       </c>
+      <c r="C16" t="s">
+        <v>2427</v>
+      </c>
       <c r="D16" s="1" t="s">
         <v>114</v>
       </c>
@@ -8338,6 +9809,9 @@
       <c r="B17" s="1">
         <v>2</v>
       </c>
+      <c r="C17" t="s">
+        <v>2428</v>
+      </c>
       <c r="D17" s="1" t="s">
         <v>123</v>
       </c>
@@ -8373,6 +9847,9 @@
       <c r="B18" s="1">
         <v>2</v>
       </c>
+      <c r="C18" t="s">
+        <v>2429</v>
+      </c>
       <c r="D18" s="1" t="s">
         <v>132</v>
       </c>
@@ -8408,6 +9885,9 @@
       <c r="B19" s="1">
         <v>2</v>
       </c>
+      <c r="C19" t="s">
+        <v>2430</v>
+      </c>
       <c r="D19" s="1" t="s">
         <v>140</v>
       </c>
@@ -8443,6 +9923,9 @@
       <c r="B20" s="1">
         <v>2</v>
       </c>
+      <c r="C20" t="s">
+        <v>2431</v>
+      </c>
       <c r="D20" s="1" t="s">
         <v>148</v>
       </c>
@@ -8478,6 +9961,9 @@
       <c r="B21" s="1">
         <v>2</v>
       </c>
+      <c r="C21" t="s">
+        <v>2432</v>
+      </c>
       <c r="D21" s="1" t="s">
         <v>157</v>
       </c>
@@ -8513,6 +9999,9 @@
       <c r="B22" s="1">
         <v>2</v>
       </c>
+      <c r="C22" t="s">
+        <v>2433</v>
+      </c>
       <c r="D22" s="1" t="s">
         <v>165</v>
       </c>
@@ -8548,6 +10037,9 @@
       <c r="B23" s="1">
         <v>2</v>
       </c>
+      <c r="C23" t="s">
+        <v>2434</v>
+      </c>
       <c r="D23" s="1" t="s">
         <v>172</v>
       </c>
@@ -8583,6 +10075,9 @@
       <c r="B24" s="1">
         <v>2</v>
       </c>
+      <c r="C24" t="s">
+        <v>2435</v>
+      </c>
       <c r="D24" s="1" t="s">
         <v>181</v>
       </c>
@@ -8618,6 +10113,9 @@
       <c r="B25" s="1">
         <v>2</v>
       </c>
+      <c r="C25" t="s">
+        <v>2436</v>
+      </c>
       <c r="D25" s="1" t="s">
         <v>190</v>
       </c>
@@ -8653,6 +10151,9 @@
       <c r="B26" s="1">
         <v>2</v>
       </c>
+      <c r="C26" t="s">
+        <v>2437</v>
+      </c>
       <c r="D26" s="1" t="s">
         <v>199</v>
       </c>
@@ -8688,6 +10189,9 @@
       <c r="B27" s="1">
         <v>2</v>
       </c>
+      <c r="C27" t="s">
+        <v>2438</v>
+      </c>
       <c r="D27" s="1" t="s">
         <v>208</v>
       </c>
@@ -8723,6 +10227,9 @@
       <c r="B28" s="1">
         <v>2</v>
       </c>
+      <c r="C28" t="s">
+        <v>2439</v>
+      </c>
       <c r="D28" s="1" t="s">
         <v>208</v>
       </c>
@@ -8758,6 +10265,9 @@
       <c r="B29" s="1">
         <v>2</v>
       </c>
+      <c r="C29" t="s">
+        <v>2440</v>
+      </c>
       <c r="D29" s="1" t="s">
         <v>219</v>
       </c>
@@ -8793,6 +10303,9 @@
       <c r="B30" s="1">
         <v>2</v>
       </c>
+      <c r="C30" t="s">
+        <v>2441</v>
+      </c>
       <c r="D30" s="1" t="s">
         <v>231</v>
       </c>
@@ -8828,6 +10341,9 @@
       <c r="B31" s="1">
         <v>2</v>
       </c>
+      <c r="C31" t="s">
+        <v>2442</v>
+      </c>
       <c r="D31" s="1" t="s">
         <v>239</v>
       </c>
@@ -8863,6 +10379,9 @@
       <c r="B32" s="1">
         <v>2</v>
       </c>
+      <c r="C32" t="s">
+        <v>2443</v>
+      </c>
       <c r="D32" s="1" t="s">
         <v>246</v>
       </c>
@@ -8898,6 +10417,9 @@
       <c r="B33" s="1">
         <v>2</v>
       </c>
+      <c r="C33" t="s">
+        <v>2444</v>
+      </c>
       <c r="D33" s="1" t="s">
         <v>250</v>
       </c>
@@ -8933,6 +10455,9 @@
       <c r="B34" s="1">
         <v>2</v>
       </c>
+      <c r="C34" t="s">
+        <v>2445</v>
+      </c>
       <c r="D34" s="1" t="s">
         <v>257</v>
       </c>
@@ -8968,6 +10493,9 @@
       <c r="B35" s="1">
         <v>2</v>
       </c>
+      <c r="C35" t="s">
+        <v>2446</v>
+      </c>
       <c r="D35" s="1" t="s">
         <v>266</v>
       </c>
@@ -9003,6 +10531,9 @@
       <c r="B36" s="1">
         <v>3</v>
       </c>
+      <c r="C36" t="s">
+        <v>2447</v>
+      </c>
       <c r="D36" s="1" t="s">
         <v>274</v>
       </c>
@@ -9038,6 +10569,9 @@
       <c r="B37" s="1">
         <v>3</v>
       </c>
+      <c r="C37" t="s">
+        <v>2448</v>
+      </c>
       <c r="D37" s="1" t="s">
         <v>283</v>
       </c>
@@ -9073,6 +10607,9 @@
       <c r="B38" s="1">
         <v>3</v>
       </c>
+      <c r="C38" t="s">
+        <v>2449</v>
+      </c>
       <c r="D38" s="1" t="s">
         <v>288</v>
       </c>
@@ -9108,6 +10645,9 @@
       <c r="B39" s="1">
         <v>3</v>
       </c>
+      <c r="C39" t="s">
+        <v>2450</v>
+      </c>
       <c r="D39" s="1" t="s">
         <v>292</v>
       </c>
@@ -9143,6 +10683,9 @@
       <c r="B40" s="1">
         <v>3</v>
       </c>
+      <c r="C40" t="s">
+        <v>2451</v>
+      </c>
       <c r="D40" s="1" t="s">
         <v>301</v>
       </c>
@@ -9178,6 +10721,9 @@
       <c r="B41" s="1">
         <v>3</v>
       </c>
+      <c r="C41" t="s">
+        <v>2452</v>
+      </c>
       <c r="D41" s="1" t="s">
         <v>308</v>
       </c>
@@ -9213,6 +10759,9 @@
       <c r="B42" s="1">
         <v>3</v>
       </c>
+      <c r="C42" t="s">
+        <v>2453</v>
+      </c>
       <c r="D42" s="1" t="s">
         <v>316</v>
       </c>
@@ -9248,6 +10797,9 @@
       <c r="B43" s="1">
         <v>3</v>
       </c>
+      <c r="C43" t="s">
+        <v>2454</v>
+      </c>
       <c r="D43" s="1" t="s">
         <v>322</v>
       </c>
@@ -9283,6 +10835,9 @@
       <c r="B44" s="1">
         <v>3</v>
       </c>
+      <c r="C44" t="s">
+        <v>2455</v>
+      </c>
       <c r="D44" s="1" t="s">
         <v>328</v>
       </c>
@@ -9318,6 +10873,9 @@
       <c r="B45" s="1">
         <v>3</v>
       </c>
+      <c r="C45" t="s">
+        <v>2456</v>
+      </c>
       <c r="D45" s="1" t="s">
         <v>334</v>
       </c>
@@ -9353,6 +10911,9 @@
       <c r="B46" s="1">
         <v>3</v>
       </c>
+      <c r="C46" t="s">
+        <v>2457</v>
+      </c>
       <c r="D46" s="1" t="s">
         <v>343</v>
       </c>
@@ -9388,6 +10949,9 @@
       <c r="B47" s="1">
         <v>3</v>
       </c>
+      <c r="C47" t="s">
+        <v>2458</v>
+      </c>
       <c r="D47" s="1" t="s">
         <v>349</v>
       </c>
@@ -9423,6 +10987,9 @@
       <c r="B48" s="1">
         <v>3</v>
       </c>
+      <c r="C48" t="s">
+        <v>2459</v>
+      </c>
       <c r="D48" s="1" t="s">
         <v>356</v>
       </c>
@@ -9458,6 +11025,9 @@
       <c r="B49" s="1">
         <v>3</v>
       </c>
+      <c r="C49" t="s">
+        <v>2460</v>
+      </c>
       <c r="D49" s="1" t="s">
         <v>362</v>
       </c>
@@ -9493,6 +11063,9 @@
       <c r="B50" s="1">
         <v>3</v>
       </c>
+      <c r="C50" t="s">
+        <v>2461</v>
+      </c>
       <c r="D50" s="1" t="s">
         <v>370</v>
       </c>
@@ -9528,6 +11101,9 @@
       <c r="B51" s="1">
         <v>3</v>
       </c>
+      <c r="C51" t="s">
+        <v>2462</v>
+      </c>
       <c r="D51" s="1" t="s">
         <v>379</v>
       </c>
@@ -9563,6 +11139,9 @@
       <c r="B52" s="1">
         <v>3</v>
       </c>
+      <c r="C52" t="s">
+        <v>2463</v>
+      </c>
       <c r="D52" s="1" t="s">
         <v>386</v>
       </c>
@@ -9598,6 +11177,9 @@
       <c r="B53" s="1">
         <v>3</v>
       </c>
+      <c r="C53" t="s">
+        <v>2464</v>
+      </c>
       <c r="D53" s="1" t="s">
         <v>394</v>
       </c>
@@ -9633,6 +11215,9 @@
       <c r="B54" s="1">
         <v>3</v>
       </c>
+      <c r="C54" t="s">
+        <v>2465</v>
+      </c>
       <c r="D54" s="1" t="s">
         <v>399</v>
       </c>
@@ -9668,6 +11253,9 @@
       <c r="B55" s="1">
         <v>3</v>
       </c>
+      <c r="C55" t="s">
+        <v>2466</v>
+      </c>
       <c r="D55" s="1" t="s">
         <v>405</v>
       </c>
@@ -9703,6 +11291,9 @@
       <c r="B56" s="1">
         <v>3</v>
       </c>
+      <c r="C56" t="s">
+        <v>2467</v>
+      </c>
       <c r="D56" s="1" t="s">
         <v>413</v>
       </c>
@@ -9738,6 +11329,9 @@
       <c r="B57" s="1">
         <v>3</v>
       </c>
+      <c r="C57" t="s">
+        <v>2468</v>
+      </c>
       <c r="D57" s="1" t="s">
         <v>413</v>
       </c>
@@ -9773,6 +11367,9 @@
       <c r="B58" s="1">
         <v>3</v>
       </c>
+      <c r="C58" t="s">
+        <v>2469</v>
+      </c>
       <c r="D58" s="1" t="s">
         <v>413</v>
       </c>
@@ -9808,6 +11405,9 @@
       <c r="B59" s="1">
         <v>3</v>
       </c>
+      <c r="C59" t="s">
+        <v>2470</v>
+      </c>
       <c r="D59" s="1" t="s">
         <v>422</v>
       </c>
@@ -9843,6 +11443,9 @@
       <c r="B60" s="1">
         <v>3</v>
       </c>
+      <c r="C60" t="s">
+        <v>2471</v>
+      </c>
       <c r="D60" s="1" t="s">
         <v>430</v>
       </c>
@@ -9878,6 +11481,9 @@
       <c r="B61" s="1">
         <v>4</v>
       </c>
+      <c r="C61" t="s">
+        <v>2472</v>
+      </c>
       <c r="D61" s="1" t="s">
         <v>439</v>
       </c>
@@ -9913,6 +11519,9 @@
       <c r="B62" s="1">
         <v>4</v>
       </c>
+      <c r="C62" t="s">
+        <v>2473</v>
+      </c>
       <c r="D62" s="1" t="s">
         <v>447</v>
       </c>
@@ -9948,6 +11557,9 @@
       <c r="B63" s="1">
         <v>4</v>
       </c>
+      <c r="C63" t="s">
+        <v>2474</v>
+      </c>
       <c r="D63" s="1" t="s">
         <v>447</v>
       </c>
@@ -9983,6 +11595,9 @@
       <c r="B64" s="1">
         <v>4</v>
       </c>
+      <c r="C64" t="s">
+        <v>2475</v>
+      </c>
       <c r="D64" s="1" t="s">
         <v>455</v>
       </c>
@@ -10018,6 +11633,9 @@
       <c r="B65" s="1">
         <v>4</v>
       </c>
+      <c r="C65" t="s">
+        <v>2476</v>
+      </c>
       <c r="D65" s="1" t="s">
         <v>463</v>
       </c>
@@ -10053,6 +11671,9 @@
       <c r="B66" s="1">
         <v>4</v>
       </c>
+      <c r="C66" t="s">
+        <v>2477</v>
+      </c>
       <c r="D66" s="1" t="s">
         <v>468</v>
       </c>
@@ -10088,6 +11709,9 @@
       <c r="B67" s="1">
         <v>4</v>
       </c>
+      <c r="C67" t="s">
+        <v>2478</v>
+      </c>
       <c r="D67" s="1" t="s">
         <v>474</v>
       </c>
@@ -10123,6 +11747,9 @@
       <c r="B68" s="1">
         <v>4</v>
       </c>
+      <c r="C68" t="s">
+        <v>2479</v>
+      </c>
       <c r="D68" s="1" t="s">
         <v>478</v>
       </c>
@@ -10158,6 +11785,9 @@
       <c r="B69" s="1">
         <v>4</v>
       </c>
+      <c r="C69" t="s">
+        <v>2480</v>
+      </c>
       <c r="D69" s="1" t="s">
         <v>484</v>
       </c>
@@ -10193,6 +11823,9 @@
       <c r="B70" s="1">
         <v>4</v>
       </c>
+      <c r="C70" t="s">
+        <v>2481</v>
+      </c>
       <c r="D70" s="1" t="s">
         <v>490</v>
       </c>
@@ -10228,6 +11861,9 @@
       <c r="B71" s="1">
         <v>4</v>
       </c>
+      <c r="C71" t="s">
+        <v>2482</v>
+      </c>
       <c r="D71" s="1" t="s">
         <v>495</v>
       </c>
@@ -10263,6 +11899,9 @@
       <c r="B72" s="1">
         <v>4</v>
       </c>
+      <c r="C72" t="s">
+        <v>2483</v>
+      </c>
       <c r="D72" s="1" t="s">
         <v>499</v>
       </c>
@@ -10298,6 +11937,9 @@
       <c r="B73" s="1">
         <v>4</v>
       </c>
+      <c r="C73" t="s">
+        <v>2484</v>
+      </c>
       <c r="D73" s="1" t="s">
         <v>507</v>
       </c>
@@ -10333,6 +11975,9 @@
       <c r="B74" s="1">
         <v>4</v>
       </c>
+      <c r="C74" t="s">
+        <v>2485</v>
+      </c>
       <c r="D74" s="1" t="s">
         <v>512</v>
       </c>
@@ -10368,6 +12013,9 @@
       <c r="B75" s="1">
         <v>4</v>
       </c>
+      <c r="C75" t="s">
+        <v>2486</v>
+      </c>
       <c r="D75" s="1" t="s">
         <v>512</v>
       </c>
@@ -10403,6 +12051,9 @@
       <c r="B76" s="1">
         <v>4</v>
       </c>
+      <c r="C76" t="s">
+        <v>2487</v>
+      </c>
       <c r="D76" s="1" t="s">
         <v>517</v>
       </c>
@@ -10438,6 +12089,9 @@
       <c r="B77" s="1">
         <v>4</v>
       </c>
+      <c r="C77" t="s">
+        <v>2488</v>
+      </c>
       <c r="D77" s="1" t="s">
         <v>521</v>
       </c>
@@ -10473,6 +12127,9 @@
       <c r="B78" s="1">
         <v>4</v>
       </c>
+      <c r="C78" t="s">
+        <v>2489</v>
+      </c>
       <c r="D78" s="1" t="s">
         <v>527</v>
       </c>
@@ -10508,6 +12165,9 @@
       <c r="B79" s="1">
         <v>4</v>
       </c>
+      <c r="C79" t="s">
+        <v>2490</v>
+      </c>
       <c r="D79" s="1" t="s">
         <v>532</v>
       </c>
@@ -10543,6 +12203,9 @@
       <c r="B80" s="1">
         <v>4</v>
       </c>
+      <c r="C80" t="s">
+        <v>2491</v>
+      </c>
       <c r="D80" s="1" t="s">
         <v>537</v>
       </c>
@@ -10578,6 +12241,9 @@
       <c r="B81" s="1">
         <v>4</v>
       </c>
+      <c r="C81" t="s">
+        <v>2492</v>
+      </c>
       <c r="D81" s="1" t="s">
         <v>542</v>
       </c>
@@ -10613,6 +12279,9 @@
       <c r="B82" s="1">
         <v>4</v>
       </c>
+      <c r="C82" t="s">
+        <v>2493</v>
+      </c>
       <c r="D82" s="1" t="s">
         <v>550</v>
       </c>
@@ -10648,6 +12317,9 @@
       <c r="B83" s="1">
         <v>4</v>
       </c>
+      <c r="C83" t="s">
+        <v>2494</v>
+      </c>
       <c r="D83" s="1" t="s">
         <v>558</v>
       </c>
@@ -10683,6 +12355,9 @@
       <c r="B84" s="1">
         <v>4</v>
       </c>
+      <c r="C84" t="s">
+        <v>2495</v>
+      </c>
       <c r="D84" s="1" t="s">
         <v>564</v>
       </c>
@@ -10718,6 +12393,9 @@
       <c r="B85" s="1">
         <v>4</v>
       </c>
+      <c r="C85" t="s">
+        <v>2496</v>
+      </c>
       <c r="D85" s="1" t="s">
         <v>568</v>
       </c>
@@ -10753,6 +12431,9 @@
       <c r="B86" s="1">
         <v>4</v>
       </c>
+      <c r="C86" t="s">
+        <v>2497</v>
+      </c>
       <c r="D86" s="1" t="s">
         <v>574</v>
       </c>
@@ -10788,6 +12469,9 @@
       <c r="B87" s="1">
         <v>4</v>
       </c>
+      <c r="C87" t="s">
+        <v>2498</v>
+      </c>
       <c r="D87" s="1" t="s">
         <v>578</v>
       </c>
@@ -10823,6 +12507,9 @@
       <c r="B88" s="1">
         <v>4</v>
       </c>
+      <c r="C88" t="s">
+        <v>2499</v>
+      </c>
       <c r="D88" s="1" t="s">
         <v>582</v>
       </c>
@@ -10858,6 +12545,9 @@
       <c r="B89" s="1">
         <v>4</v>
       </c>
+      <c r="C89" t="s">
+        <v>2500</v>
+      </c>
       <c r="D89" s="1" t="s">
         <v>468</v>
       </c>
@@ -10893,6 +12583,9 @@
       <c r="B90" s="1">
         <v>4</v>
       </c>
+      <c r="C90" t="s">
+        <v>2501</v>
+      </c>
       <c r="D90" s="1" t="s">
         <v>474</v>
       </c>
@@ -10928,6 +12621,9 @@
       <c r="B91" s="1">
         <v>4</v>
       </c>
+      <c r="C91" t="s">
+        <v>2502</v>
+      </c>
       <c r="D91" s="1" t="s">
         <v>587</v>
       </c>
@@ -10963,6 +12659,9 @@
       <c r="B92" s="1">
         <v>4</v>
       </c>
+      <c r="C92" t="s">
+        <v>2503</v>
+      </c>
       <c r="D92" s="1" t="s">
         <v>592</v>
       </c>
@@ -10998,6 +12697,9 @@
       <c r="B93" s="1">
         <v>4</v>
       </c>
+      <c r="C93" t="s">
+        <v>2504</v>
+      </c>
       <c r="D93" s="1" t="s">
         <v>596</v>
       </c>
@@ -11033,6 +12735,9 @@
       <c r="B94" s="1">
         <v>4</v>
       </c>
+      <c r="C94" t="s">
+        <v>2505</v>
+      </c>
       <c r="D94" s="1" t="s">
         <v>604</v>
       </c>
@@ -11068,6 +12773,9 @@
       <c r="B95" s="1">
         <v>4</v>
       </c>
+      <c r="C95" t="s">
+        <v>2506</v>
+      </c>
       <c r="D95" s="1" t="s">
         <v>604</v>
       </c>
@@ -11103,6 +12811,9 @@
       <c r="B96" s="1">
         <v>4</v>
       </c>
+      <c r="C96" t="s">
+        <v>2507</v>
+      </c>
       <c r="D96" s="1" t="s">
         <v>621</v>
       </c>
@@ -11138,6 +12849,9 @@
       <c r="B97" s="1">
         <v>5</v>
       </c>
+      <c r="C97" t="s">
+        <v>2508</v>
+      </c>
       <c r="D97" s="1" t="s">
         <v>630</v>
       </c>
@@ -11173,6 +12887,9 @@
       <c r="B98" s="1">
         <v>5</v>
       </c>
+      <c r="C98" t="s">
+        <v>2509</v>
+      </c>
       <c r="D98" s="1" t="s">
         <v>634</v>
       </c>
@@ -11208,6 +12925,9 @@
       <c r="B99" s="1">
         <v>5</v>
       </c>
+      <c r="C99" t="s">
+        <v>2510</v>
+      </c>
       <c r="D99" s="1" t="s">
         <v>634</v>
       </c>
@@ -11243,6 +12963,9 @@
       <c r="B100" s="1">
         <v>5</v>
       </c>
+      <c r="C100" t="s">
+        <v>2511</v>
+      </c>
       <c r="D100" s="1" t="s">
         <v>640</v>
       </c>
@@ -11278,6 +13001,9 @@
       <c r="B101" s="1">
         <v>5</v>
       </c>
+      <c r="C101" t="s">
+        <v>2512</v>
+      </c>
       <c r="D101" s="1" t="s">
         <v>646</v>
       </c>
@@ -11313,6 +13039,9 @@
       <c r="B102" s="1">
         <v>5</v>
       </c>
+      <c r="C102" t="s">
+        <v>2513</v>
+      </c>
       <c r="D102" s="1" t="s">
         <v>652</v>
       </c>
@@ -11348,6 +13077,9 @@
       <c r="B103" s="1">
         <v>5</v>
       </c>
+      <c r="C103" t="s">
+        <v>2514</v>
+      </c>
       <c r="D103" s="1" t="s">
         <v>657</v>
       </c>
@@ -11383,6 +13115,9 @@
       <c r="B104" s="1">
         <v>5</v>
       </c>
+      <c r="C104" t="s">
+        <v>2515</v>
+      </c>
       <c r="D104" s="1" t="s">
         <v>661</v>
       </c>
@@ -11418,6 +13153,9 @@
       <c r="B105" s="1">
         <v>5</v>
       </c>
+      <c r="C105" t="s">
+        <v>2516</v>
+      </c>
       <c r="D105" s="1" t="s">
         <v>666</v>
       </c>
@@ -11453,6 +13191,9 @@
       <c r="B106" s="1">
         <v>5</v>
       </c>
+      <c r="C106" t="s">
+        <v>2517</v>
+      </c>
       <c r="D106" s="1" t="s">
         <v>672</v>
       </c>
@@ -11488,6 +13229,9 @@
       <c r="B107" s="1">
         <v>5</v>
       </c>
+      <c r="C107" t="s">
+        <v>2518</v>
+      </c>
       <c r="D107" s="1" t="s">
         <v>676</v>
       </c>
@@ -11523,6 +13267,9 @@
       <c r="B108" s="1">
         <v>5</v>
       </c>
+      <c r="C108" t="s">
+        <v>2519</v>
+      </c>
       <c r="D108" s="1" t="s">
         <v>680</v>
       </c>
@@ -11558,6 +13305,9 @@
       <c r="B109" s="1">
         <v>5</v>
       </c>
+      <c r="C109" t="s">
+        <v>2520</v>
+      </c>
       <c r="D109" s="1" t="s">
         <v>686</v>
       </c>
@@ -11593,6 +13343,9 @@
       <c r="B110" s="1">
         <v>5</v>
       </c>
+      <c r="C110" t="s">
+        <v>2521</v>
+      </c>
       <c r="D110" s="1" t="s">
         <v>690</v>
       </c>
@@ -11628,6 +13381,9 @@
       <c r="B111" s="1">
         <v>5</v>
       </c>
+      <c r="C111" t="s">
+        <v>2522</v>
+      </c>
       <c r="D111" s="1" t="s">
         <v>694</v>
       </c>
@@ -11663,6 +13419,9 @@
       <c r="B112" s="1">
         <v>5</v>
       </c>
+      <c r="C112" t="s">
+        <v>2523</v>
+      </c>
       <c r="D112" s="1" t="s">
         <v>701</v>
       </c>
@@ -11698,6 +13457,9 @@
       <c r="B113" s="1">
         <v>5</v>
       </c>
+      <c r="C113" t="s">
+        <v>2524</v>
+      </c>
       <c r="D113" s="1" t="s">
         <v>705</v>
       </c>
@@ -11733,6 +13495,9 @@
       <c r="B114" s="1">
         <v>5</v>
       </c>
+      <c r="C114" t="s">
+        <v>2525</v>
+      </c>
       <c r="D114" s="1" t="s">
         <v>709</v>
       </c>
@@ -11768,6 +13533,9 @@
       <c r="B115" s="1">
         <v>5</v>
       </c>
+      <c r="C115" t="s">
+        <v>2526</v>
+      </c>
       <c r="D115" s="1" t="s">
         <v>712</v>
       </c>
@@ -11803,6 +13571,9 @@
       <c r="B116" s="1">
         <v>5</v>
       </c>
+      <c r="C116" t="s">
+        <v>2527</v>
+      </c>
       <c r="D116" s="1" t="s">
         <v>715</v>
       </c>
@@ -11838,6 +13609,9 @@
       <c r="B117" s="1">
         <v>5</v>
       </c>
+      <c r="C117" t="s">
+        <v>2528</v>
+      </c>
       <c r="D117" s="1" t="s">
         <v>715</v>
       </c>
@@ -11873,6 +13647,9 @@
       <c r="B118" s="1">
         <v>5</v>
       </c>
+      <c r="C118" t="s">
+        <v>2529</v>
+      </c>
       <c r="D118" s="1" t="s">
         <v>721</v>
       </c>
@@ -11908,6 +13685,9 @@
       <c r="B119" s="1">
         <v>5</v>
       </c>
+      <c r="C119" t="s">
+        <v>2530</v>
+      </c>
       <c r="D119" s="1" t="s">
         <v>721</v>
       </c>
@@ -11943,6 +13723,9 @@
       <c r="B120" s="1">
         <v>5</v>
       </c>
+      <c r="C120" t="s">
+        <v>2531</v>
+      </c>
       <c r="D120" s="1" t="s">
         <v>725</v>
       </c>
@@ -11978,6 +13761,9 @@
       <c r="B121" s="1">
         <v>5</v>
       </c>
+      <c r="C121" t="s">
+        <v>2532</v>
+      </c>
       <c r="D121" s="1" t="s">
         <v>729</v>
       </c>
@@ -12013,6 +13799,9 @@
       <c r="B122" s="1">
         <v>5</v>
       </c>
+      <c r="C122" t="s">
+        <v>2533</v>
+      </c>
       <c r="D122" s="1" t="s">
         <v>734</v>
       </c>
@@ -12048,6 +13837,9 @@
       <c r="B123" s="1">
         <v>5</v>
       </c>
+      <c r="C123" t="s">
+        <v>2534</v>
+      </c>
       <c r="D123" s="1" t="s">
         <v>738</v>
       </c>
@@ -12083,6 +13875,9 @@
       <c r="B124" s="1">
         <v>5</v>
       </c>
+      <c r="C124" t="s">
+        <v>2535</v>
+      </c>
       <c r="D124" s="1" t="s">
         <v>742</v>
       </c>
@@ -12118,6 +13913,9 @@
       <c r="B125" s="1">
         <v>5</v>
       </c>
+      <c r="C125" t="s">
+        <v>2536</v>
+      </c>
       <c r="D125" s="1" t="s">
         <v>746</v>
       </c>
@@ -12153,6 +13951,9 @@
       <c r="B126" s="1">
         <v>5</v>
       </c>
+      <c r="C126" t="s">
+        <v>2537</v>
+      </c>
       <c r="D126" s="1" t="s">
         <v>751</v>
       </c>
@@ -12188,6 +13989,9 @@
       <c r="B127" s="1">
         <v>5</v>
       </c>
+      <c r="C127" t="s">
+        <v>2538</v>
+      </c>
       <c r="D127" s="1" t="s">
         <v>756</v>
       </c>
@@ -12223,6 +14027,9 @@
       <c r="B128" s="1">
         <v>5</v>
       </c>
+      <c r="C128" t="s">
+        <v>2539</v>
+      </c>
       <c r="D128" s="1" t="s">
         <v>761</v>
       </c>
@@ -12258,6 +14065,9 @@
       <c r="B129" s="1">
         <v>5</v>
       </c>
+      <c r="C129" t="s">
+        <v>2540</v>
+      </c>
       <c r="D129" s="1" t="s">
         <v>765</v>
       </c>
@@ -12293,6 +14103,9 @@
       <c r="B130" s="1">
         <v>5</v>
       </c>
+      <c r="C130" t="s">
+        <v>2541</v>
+      </c>
       <c r="D130" s="1" t="s">
         <v>771</v>
       </c>
@@ -12328,6 +14141,9 @@
       <c r="B131" s="1">
         <v>5</v>
       </c>
+      <c r="C131" t="s">
+        <v>2542</v>
+      </c>
       <c r="D131" s="1" t="s">
         <v>776</v>
       </c>
@@ -12363,6 +14179,9 @@
       <c r="B132" s="1">
         <v>5</v>
       </c>
+      <c r="C132" t="s">
+        <v>2543</v>
+      </c>
       <c r="D132" s="1" t="s">
         <v>776</v>
       </c>
@@ -12398,6 +14217,9 @@
       <c r="B133" s="1">
         <v>5</v>
       </c>
+      <c r="C133" t="s">
+        <v>2544</v>
+      </c>
       <c r="D133" s="1" t="s">
         <v>785</v>
       </c>
@@ -12433,6 +14255,9 @@
       <c r="B134" s="1">
         <v>5</v>
       </c>
+      <c r="C134" t="s">
+        <v>2545</v>
+      </c>
       <c r="D134" s="1" t="s">
         <v>791</v>
       </c>
@@ -12468,6 +14293,9 @@
       <c r="B135" s="1">
         <v>5</v>
       </c>
+      <c r="C135" t="s">
+        <v>2546</v>
+      </c>
       <c r="D135" s="1" t="s">
         <v>796</v>
       </c>
@@ -12503,6 +14331,9 @@
       <c r="B136" s="1">
         <v>5</v>
       </c>
+      <c r="C136" t="s">
+        <v>2547</v>
+      </c>
       <c r="D136" s="1" t="s">
         <v>796</v>
       </c>
@@ -12538,6 +14369,9 @@
       <c r="B137" s="1">
         <v>5</v>
       </c>
+      <c r="C137" t="s">
+        <v>2548</v>
+      </c>
       <c r="D137" s="1" t="s">
         <v>803</v>
       </c>
@@ -12573,6 +14407,9 @@
       <c r="B138" s="1">
         <v>5</v>
       </c>
+      <c r="C138" t="s">
+        <v>2549</v>
+      </c>
       <c r="D138" s="1" t="s">
         <v>809</v>
       </c>
@@ -12608,6 +14445,9 @@
       <c r="B139" s="1">
         <v>6</v>
       </c>
+      <c r="C139" t="s">
+        <v>2550</v>
+      </c>
       <c r="D139" s="1" t="s">
         <v>818</v>
       </c>
@@ -12643,6 +14483,9 @@
       <c r="B140" s="1">
         <v>6</v>
       </c>
+      <c r="C140" t="s">
+        <v>2551</v>
+      </c>
       <c r="D140" s="1" t="s">
         <v>826</v>
       </c>
@@ -12678,6 +14521,9 @@
       <c r="B141" s="1">
         <v>6</v>
       </c>
+      <c r="C141" t="s">
+        <v>2552</v>
+      </c>
       <c r="D141" s="1" t="s">
         <v>832</v>
       </c>
@@ -12713,6 +14559,9 @@
       <c r="B142" s="1">
         <v>6</v>
       </c>
+      <c r="C142" t="s">
+        <v>2553</v>
+      </c>
       <c r="D142" s="1" t="s">
         <v>838</v>
       </c>
@@ -12748,6 +14597,9 @@
       <c r="B143" s="1">
         <v>7</v>
       </c>
+      <c r="C143" t="s">
+        <v>2554</v>
+      </c>
       <c r="D143" s="1" t="s">
         <v>844</v>
       </c>
@@ -12783,6 +14635,9 @@
       <c r="B144" s="1">
         <v>7</v>
       </c>
+      <c r="C144" t="s">
+        <v>2555</v>
+      </c>
       <c r="D144" s="1" t="s">
         <v>851</v>
       </c>
@@ -12818,6 +14673,9 @@
       <c r="B145" s="1">
         <v>7</v>
       </c>
+      <c r="C145" t="s">
+        <v>2556</v>
+      </c>
       <c r="D145" s="1" t="s">
         <v>856</v>
       </c>
@@ -12853,6 +14711,9 @@
       <c r="B146" s="1">
         <v>7</v>
       </c>
+      <c r="C146" t="s">
+        <v>2557</v>
+      </c>
       <c r="D146" s="1" t="s">
         <v>860</v>
       </c>
@@ -12888,6 +14749,9 @@
       <c r="B147" s="1">
         <v>7</v>
       </c>
+      <c r="C147" t="s">
+        <v>2558</v>
+      </c>
       <c r="D147" s="1" t="s">
         <v>860</v>
       </c>
@@ -12923,6 +14787,9 @@
       <c r="B148" s="1">
         <v>7</v>
       </c>
+      <c r="C148" t="s">
+        <v>2559</v>
+      </c>
       <c r="D148" s="1" t="s">
         <v>868</v>
       </c>
@@ -12958,6 +14825,9 @@
       <c r="B149" s="1">
         <v>7</v>
       </c>
+      <c r="C149" t="s">
+        <v>2560</v>
+      </c>
       <c r="D149" s="1" t="s">
         <v>873</v>
       </c>
@@ -12993,6 +14863,9 @@
       <c r="B150" s="1">
         <v>7</v>
       </c>
+      <c r="C150" t="s">
+        <v>2561</v>
+      </c>
       <c r="D150" s="1" t="s">
         <v>878</v>
       </c>
@@ -13028,6 +14901,9 @@
       <c r="B151" s="1">
         <v>7</v>
       </c>
+      <c r="C151" t="s">
+        <v>2562</v>
+      </c>
       <c r="D151" s="1" t="s">
         <v>882</v>
       </c>
@@ -13063,6 +14939,9 @@
       <c r="B152" s="1">
         <v>7</v>
       </c>
+      <c r="C152" t="s">
+        <v>2563</v>
+      </c>
       <c r="D152" s="1" t="s">
         <v>886</v>
       </c>
@@ -13098,6 +14977,9 @@
       <c r="B153" s="1">
         <v>7</v>
       </c>
+      <c r="C153" t="s">
+        <v>2564</v>
+      </c>
       <c r="D153" s="1" t="s">
         <v>890</v>
       </c>
@@ -13133,6 +15015,9 @@
       <c r="B154" s="1">
         <v>7</v>
       </c>
+      <c r="C154" t="s">
+        <v>2565</v>
+      </c>
       <c r="D154" s="1" t="s">
         <v>895</v>
       </c>
@@ -13168,6 +15053,9 @@
       <c r="B155" s="1">
         <v>7</v>
       </c>
+      <c r="C155" t="s">
+        <v>2566</v>
+      </c>
       <c r="D155" s="1" t="s">
         <v>901</v>
       </c>
@@ -13203,6 +15091,9 @@
       <c r="B156" s="1">
         <v>7</v>
       </c>
+      <c r="C156" t="s">
+        <v>2567</v>
+      </c>
       <c r="D156" s="1" t="s">
         <v>882</v>
       </c>
@@ -13238,6 +15129,9 @@
       <c r="B157" s="1">
         <v>7</v>
       </c>
+      <c r="C157" t="s">
+        <v>2568</v>
+      </c>
       <c r="D157" s="1" t="s">
         <v>909</v>
       </c>
@@ -13273,6 +15167,9 @@
       <c r="B158" s="1">
         <v>7</v>
       </c>
+      <c r="C158" t="s">
+        <v>2569</v>
+      </c>
       <c r="D158" s="1" t="s">
         <v>913</v>
       </c>
@@ -13308,6 +15205,9 @@
       <c r="B159" s="1">
         <v>7</v>
       </c>
+      <c r="C159" t="s">
+        <v>2570</v>
+      </c>
       <c r="D159" s="1" t="s">
         <v>918</v>
       </c>
@@ -13343,6 +15243,9 @@
       <c r="B160" s="1">
         <v>8</v>
       </c>
+      <c r="C160" t="s">
+        <v>2571</v>
+      </c>
       <c r="D160" s="1" t="s">
         <v>923</v>
       </c>
@@ -13378,6 +15281,9 @@
       <c r="B161" s="1">
         <v>8</v>
       </c>
+      <c r="C161" t="s">
+        <v>2572</v>
+      </c>
       <c r="D161" s="1" t="s">
         <v>929</v>
       </c>
@@ -13413,6 +15319,9 @@
       <c r="B162" s="1">
         <v>8</v>
       </c>
+      <c r="C162" t="s">
+        <v>2573</v>
+      </c>
       <c r="D162" s="1" t="s">
         <v>934</v>
       </c>
@@ -13448,6 +15357,9 @@
       <c r="B163" s="1">
         <v>8</v>
       </c>
+      <c r="C163" t="s">
+        <v>2574</v>
+      </c>
       <c r="D163" s="1" t="s">
         <v>936</v>
       </c>
@@ -13483,6 +15395,9 @@
       <c r="B164" s="1">
         <v>8</v>
       </c>
+      <c r="C164" t="s">
+        <v>2575</v>
+      </c>
       <c r="D164" s="1" t="s">
         <v>941</v>
       </c>
@@ -13518,6 +15433,9 @@
       <c r="B165" s="1">
         <v>8</v>
       </c>
+      <c r="C165" t="s">
+        <v>2576</v>
+      </c>
       <c r="D165" s="1" t="s">
         <v>947</v>
       </c>
@@ -13553,6 +15471,9 @@
       <c r="B166" s="1">
         <v>8</v>
       </c>
+      <c r="C166" t="s">
+        <v>2577</v>
+      </c>
       <c r="D166" s="1" t="s">
         <v>952</v>
       </c>
@@ -13588,6 +15509,9 @@
       <c r="B167" s="1">
         <v>8</v>
       </c>
+      <c r="C167" t="s">
+        <v>2578</v>
+      </c>
       <c r="D167" s="1" t="s">
         <v>956</v>
       </c>
@@ -13623,6 +15547,9 @@
       <c r="B168" s="1">
         <v>8</v>
       </c>
+      <c r="C168" t="s">
+        <v>2579</v>
+      </c>
       <c r="D168" s="1" t="s">
         <v>964</v>
       </c>
@@ -13658,6 +15585,9 @@
       <c r="B169" s="1">
         <v>8</v>
       </c>
+      <c r="C169" t="s">
+        <v>2580</v>
+      </c>
       <c r="D169" s="1" t="s">
         <v>967</v>
       </c>
@@ -13693,6 +15623,9 @@
       <c r="B170" s="1">
         <v>8</v>
       </c>
+      <c r="C170" t="s">
+        <v>2581</v>
+      </c>
       <c r="D170" s="1" t="s">
         <v>972</v>
       </c>
@@ -13728,6 +15661,9 @@
       <c r="B171" s="1">
         <v>8</v>
       </c>
+      <c r="C171" t="s">
+        <v>2582</v>
+      </c>
       <c r="D171" s="1" t="s">
         <v>977</v>
       </c>
@@ -13763,6 +15699,9 @@
       <c r="B172" s="1">
         <v>8</v>
       </c>
+      <c r="C172" t="s">
+        <v>2583</v>
+      </c>
       <c r="D172" s="1" t="s">
         <v>984</v>
       </c>
@@ -13798,6 +15737,9 @@
       <c r="B173" s="1">
         <v>8</v>
       </c>
+      <c r="C173" t="s">
+        <v>2584</v>
+      </c>
       <c r="D173" s="1" t="s">
         <v>990</v>
       </c>
@@ -13833,6 +15775,9 @@
       <c r="B174" s="1">
         <v>8</v>
       </c>
+      <c r="C174" t="s">
+        <v>2585</v>
+      </c>
       <c r="D174" s="1" t="s">
         <v>994</v>
       </c>
@@ -13868,6 +15813,9 @@
       <c r="B175" s="1">
         <v>8</v>
       </c>
+      <c r="C175" t="s">
+        <v>2586</v>
+      </c>
       <c r="D175" s="1" t="s">
         <v>998</v>
       </c>
@@ -13903,6 +15851,9 @@
       <c r="B176" s="1">
         <v>8</v>
       </c>
+      <c r="C176" t="s">
+        <v>2587</v>
+      </c>
       <c r="D176" s="1" t="s">
         <v>1002</v>
       </c>
@@ -13938,6 +15889,9 @@
       <c r="B177" s="1">
         <v>8</v>
       </c>
+      <c r="C177" t="s">
+        <v>2588</v>
+      </c>
       <c r="D177" s="1" t="s">
         <v>1008</v>
       </c>
@@ -13973,6 +15927,9 @@
       <c r="B178" s="1">
         <v>8</v>
       </c>
+      <c r="C178" t="s">
+        <v>2589</v>
+      </c>
       <c r="D178" s="1" t="s">
         <v>1012</v>
       </c>
@@ -14008,6 +15965,9 @@
       <c r="B179" s="1">
         <v>8</v>
       </c>
+      <c r="C179" t="s">
+        <v>2590</v>
+      </c>
       <c r="D179" s="1" t="s">
         <v>1017</v>
       </c>
@@ -14043,6 +16003,9 @@
       <c r="B180" s="1">
         <v>8</v>
       </c>
+      <c r="C180" t="s">
+        <v>2591</v>
+      </c>
       <c r="D180" s="1" t="s">
         <v>1022</v>
       </c>
@@ -14078,6 +16041,9 @@
       <c r="B181" s="1">
         <v>8</v>
       </c>
+      <c r="C181" t="s">
+        <v>2592</v>
+      </c>
       <c r="D181" s="1" t="s">
         <v>1027</v>
       </c>
@@ -14113,6 +16079,9 @@
       <c r="B182" s="1">
         <v>8</v>
       </c>
+      <c r="C182" t="s">
+        <v>2593</v>
+      </c>
       <c r="D182" s="1" t="s">
         <v>1032</v>
       </c>
@@ -14148,6 +16117,9 @@
       <c r="B183" s="1">
         <v>8</v>
       </c>
+      <c r="C183" t="s">
+        <v>2594</v>
+      </c>
       <c r="D183" s="1" t="s">
         <v>1037</v>
       </c>
@@ -14183,6 +16155,9 @@
       <c r="B184" s="1">
         <v>8</v>
       </c>
+      <c r="C184" t="s">
+        <v>2595</v>
+      </c>
       <c r="D184" s="1" t="s">
         <v>1043</v>
       </c>
@@ -14218,6 +16193,9 @@
       <c r="B185" s="1">
         <v>8</v>
       </c>
+      <c r="C185" t="s">
+        <v>2596</v>
+      </c>
       <c r="D185" s="1" t="s">
         <v>1047</v>
       </c>
@@ -14253,6 +16231,9 @@
       <c r="B186" s="1">
         <v>8</v>
       </c>
+      <c r="C186" t="s">
+        <v>2597</v>
+      </c>
       <c r="D186" s="1" t="s">
         <v>1054</v>
       </c>
@@ -14288,6 +16269,9 @@
       <c r="B187" s="1">
         <v>8</v>
       </c>
+      <c r="C187" t="s">
+        <v>2598</v>
+      </c>
       <c r="D187" s="1" t="s">
         <v>1057</v>
       </c>
@@ -14323,6 +16307,9 @@
       <c r="B188" s="1">
         <v>8</v>
       </c>
+      <c r="C188" t="s">
+        <v>2599</v>
+      </c>
       <c r="D188" s="1" t="s">
         <v>1064</v>
       </c>
@@ -14358,6 +16345,9 @@
       <c r="B189" s="1">
         <v>8</v>
       </c>
+      <c r="C189" t="s">
+        <v>2600</v>
+      </c>
       <c r="D189" s="1" t="s">
         <v>1072</v>
       </c>
@@ -14393,6 +16383,9 @@
       <c r="B190" s="1">
         <v>8</v>
       </c>
+      <c r="C190" t="s">
+        <v>2601</v>
+      </c>
       <c r="D190" s="1" t="s">
         <v>1078</v>
       </c>
@@ -14428,6 +16421,9 @@
       <c r="B191" s="1">
         <v>8</v>
       </c>
+      <c r="C191" t="s">
+        <v>2602</v>
+      </c>
       <c r="D191" s="1" t="s">
         <v>1083</v>
       </c>
@@ -14463,6 +16459,9 @@
       <c r="B192" s="1">
         <v>8</v>
       </c>
+      <c r="C192" t="s">
+        <v>2603</v>
+      </c>
       <c r="D192" s="1" t="s">
         <v>1083</v>
       </c>
@@ -14498,6 +16497,9 @@
       <c r="B193" s="1">
         <v>8</v>
       </c>
+      <c r="C193" t="s">
+        <v>2604</v>
+      </c>
       <c r="D193" s="1" t="s">
         <v>1093</v>
       </c>
@@ -14533,6 +16535,9 @@
       <c r="B194" s="1">
         <v>8</v>
       </c>
+      <c r="C194" t="s">
+        <v>2605</v>
+      </c>
       <c r="D194" s="1" t="s">
         <v>1099</v>
       </c>
@@ -14568,6 +16573,9 @@
       <c r="B195" s="1">
         <v>8</v>
       </c>
+      <c r="C195" t="s">
+        <v>2606</v>
+      </c>
       <c r="D195" s="1" t="s">
         <v>1109</v>
       </c>
@@ -14603,6 +16611,9 @@
       <c r="B196" s="1">
         <v>8</v>
       </c>
+      <c r="C196" t="s">
+        <v>2607</v>
+      </c>
       <c r="D196" s="1" t="s">
         <v>1114</v>
       </c>
@@ -14638,6 +16649,9 @@
       <c r="B197" s="1">
         <v>8</v>
       </c>
+      <c r="C197" t="s">
+        <v>2608</v>
+      </c>
       <c r="D197" s="1" t="s">
         <v>1120</v>
       </c>
@@ -14673,6 +16687,9 @@
       <c r="B198" s="1">
         <v>8</v>
       </c>
+      <c r="C198" t="s">
+        <v>2609</v>
+      </c>
       <c r="D198" s="1" t="s">
         <v>1126</v>
       </c>
@@ -14708,6 +16725,9 @@
       <c r="B199" s="1">
         <v>8</v>
       </c>
+      <c r="C199" t="s">
+        <v>2610</v>
+      </c>
       <c r="D199" s="1" t="s">
         <v>1133</v>
       </c>
@@ -14743,6 +16763,9 @@
       <c r="B200" s="1">
         <v>8</v>
       </c>
+      <c r="C200" t="s">
+        <v>2611</v>
+      </c>
       <c r="D200" s="1" t="s">
         <v>1137</v>
       </c>
@@ -14778,6 +16801,9 @@
       <c r="B201" s="1">
         <v>8</v>
       </c>
+      <c r="C201" t="s">
+        <v>2612</v>
+      </c>
       <c r="D201" s="1" t="s">
         <v>1142</v>
       </c>
@@ -14813,6 +16839,9 @@
       <c r="B202" s="1">
         <v>9</v>
       </c>
+      <c r="C202" t="s">
+        <v>2613</v>
+      </c>
       <c r="D202" s="1" t="s">
         <v>1148</v>
       </c>
@@ -14848,6 +16877,9 @@
       <c r="B203" s="1">
         <v>9</v>
       </c>
+      <c r="C203" t="s">
+        <v>2614</v>
+      </c>
       <c r="D203" s="1" t="s">
         <v>1156</v>
       </c>
@@ -14883,6 +16915,9 @@
       <c r="B204" s="1">
         <v>9</v>
       </c>
+      <c r="C204" t="s">
+        <v>2615</v>
+      </c>
       <c r="D204" s="1" t="s">
         <v>1160</v>
       </c>
@@ -14918,6 +16953,9 @@
       <c r="B205" s="1">
         <v>9</v>
       </c>
+      <c r="C205" t="s">
+        <v>2616</v>
+      </c>
       <c r="D205" s="1" t="s">
         <v>1164</v>
       </c>
@@ -14953,6 +16991,9 @@
       <c r="B206" s="1">
         <v>9</v>
       </c>
+      <c r="C206" t="s">
+        <v>2617</v>
+      </c>
       <c r="D206" s="1" t="s">
         <v>1171</v>
       </c>
@@ -14988,6 +17029,9 @@
       <c r="B207" s="1">
         <v>9</v>
       </c>
+      <c r="C207" t="s">
+        <v>2618</v>
+      </c>
       <c r="D207" s="1" t="s">
         <v>1176</v>
       </c>
@@ -15023,6 +17067,9 @@
       <c r="B208" s="1">
         <v>9</v>
       </c>
+      <c r="C208" t="s">
+        <v>2619</v>
+      </c>
       <c r="D208" s="1" t="s">
         <v>1183</v>
       </c>
@@ -15058,6 +17105,9 @@
       <c r="B209" s="1">
         <v>9</v>
       </c>
+      <c r="C209" t="s">
+        <v>2620</v>
+      </c>
       <c r="D209" s="1" t="s">
         <v>1190</v>
       </c>
@@ -15093,6 +17143,9 @@
       <c r="B210" s="1">
         <v>9</v>
       </c>
+      <c r="C210" t="s">
+        <v>2621</v>
+      </c>
       <c r="D210" s="1" t="s">
         <v>1197</v>
       </c>
@@ -15128,6 +17181,9 @@
       <c r="B211" s="1">
         <v>10</v>
       </c>
+      <c r="C211" t="s">
+        <v>2622</v>
+      </c>
       <c r="D211" s="1" t="s">
         <v>1201</v>
       </c>
@@ -15163,6 +17219,9 @@
       <c r="B212" s="1">
         <v>10</v>
       </c>
+      <c r="C212" t="s">
+        <v>2623</v>
+      </c>
       <c r="D212" s="1" t="s">
         <v>1205</v>
       </c>
@@ -15198,6 +17257,9 @@
       <c r="B213" s="1">
         <v>10</v>
       </c>
+      <c r="C213" t="s">
+        <v>2624</v>
+      </c>
       <c r="D213" s="1" t="s">
         <v>1205</v>
       </c>
@@ -15233,6 +17295,9 @@
       <c r="B214" s="1">
         <v>10</v>
       </c>
+      <c r="C214" t="s">
+        <v>2625</v>
+      </c>
       <c r="D214" s="1" t="s">
         <v>1211</v>
       </c>
@@ -15268,6 +17333,9 @@
       <c r="B215" s="1">
         <v>10</v>
       </c>
+      <c r="C215" t="s">
+        <v>2626</v>
+      </c>
       <c r="D215" s="1" t="s">
         <v>1211</v>
       </c>
@@ -15303,6 +17371,9 @@
       <c r="B216" s="1">
         <v>11</v>
       </c>
+      <c r="C216" t="s">
+        <v>2627</v>
+      </c>
       <c r="D216" s="1" t="s">
         <v>1217</v>
       </c>
@@ -15338,6 +17409,9 @@
       <c r="B217" s="1">
         <v>11</v>
       </c>
+      <c r="C217" t="s">
+        <v>2628</v>
+      </c>
       <c r="D217" s="1" t="s">
         <v>1224</v>
       </c>
@@ -15373,6 +17447,9 @@
       <c r="B218" s="1">
         <v>11</v>
       </c>
+      <c r="C218" t="s">
+        <v>2629</v>
+      </c>
       <c r="D218" s="1" t="s">
         <v>1228</v>
       </c>
@@ -15408,6 +17485,9 @@
       <c r="B219" s="1">
         <v>11</v>
       </c>
+      <c r="C219" t="s">
+        <v>2630</v>
+      </c>
       <c r="D219" s="1" t="s">
         <v>1232</v>
       </c>
@@ -15443,6 +17523,9 @@
       <c r="B220" s="1">
         <v>11</v>
       </c>
+      <c r="C220" t="s">
+        <v>2631</v>
+      </c>
       <c r="D220" s="1" t="s">
         <v>1236</v>
       </c>
@@ -15478,6 +17561,9 @@
       <c r="B221" s="1">
         <v>12</v>
       </c>
+      <c r="C221" t="s">
+        <v>2632</v>
+      </c>
       <c r="D221" s="1" t="s">
         <v>1240</v>
       </c>
@@ -15513,6 +17599,9 @@
       <c r="B222" s="1">
         <v>12</v>
       </c>
+      <c r="C222" t="s">
+        <v>2633</v>
+      </c>
       <c r="D222" s="1" t="s">
         <v>1240</v>
       </c>
@@ -15548,6 +17637,9 @@
       <c r="B223" s="1">
         <v>13</v>
       </c>
+      <c r="C223" t="s">
+        <v>2634</v>
+      </c>
       <c r="D223" s="1" t="s">
         <v>1248</v>
       </c>
@@ -15583,6 +17675,9 @@
       <c r="B224" s="1">
         <v>13</v>
       </c>
+      <c r="C224" t="s">
+        <v>2635</v>
+      </c>
       <c r="D224" s="1" t="s">
         <v>1248</v>
       </c>
@@ -15618,6 +17713,9 @@
       <c r="B225" s="1">
         <v>13</v>
       </c>
+      <c r="C225" t="s">
+        <v>2636</v>
+      </c>
       <c r="D225" s="1" t="s">
         <v>1256</v>
       </c>
@@ -15653,6 +17751,9 @@
       <c r="B226" s="1">
         <v>14</v>
       </c>
+      <c r="C226" t="s">
+        <v>2637</v>
+      </c>
       <c r="D226" s="1" t="s">
         <v>1260</v>
       </c>
@@ -15688,6 +17789,9 @@
       <c r="B227" s="1">
         <v>14</v>
       </c>
+      <c r="C227" t="s">
+        <v>2638</v>
+      </c>
       <c r="D227" s="1" t="s">
         <v>1267</v>
       </c>
@@ -15723,6 +17827,9 @@
       <c r="B228" s="1">
         <v>14</v>
       </c>
+      <c r="C228" t="s">
+        <v>2639</v>
+      </c>
       <c r="D228" s="1" t="s">
         <v>1272</v>
       </c>
@@ -15758,6 +17865,9 @@
       <c r="B229" s="1">
         <v>14</v>
       </c>
+      <c r="C229" t="s">
+        <v>2640</v>
+      </c>
       <c r="D229" s="1" t="s">
         <v>1276</v>
       </c>
@@ -15793,6 +17903,9 @@
       <c r="B230" s="1">
         <v>14</v>
       </c>
+      <c r="C230" t="s">
+        <v>2641</v>
+      </c>
       <c r="D230" s="1" t="s">
         <v>1276</v>
       </c>
@@ -15828,6 +17941,9 @@
       <c r="B231" s="1">
         <v>14</v>
       </c>
+      <c r="C231" t="s">
+        <v>2642</v>
+      </c>
       <c r="D231" s="1" t="s">
         <v>1280</v>
       </c>
@@ -15863,6 +17979,9 @@
       <c r="B232" s="1">
         <v>14</v>
       </c>
+      <c r="C232" t="s">
+        <v>2643</v>
+      </c>
       <c r="D232" s="1" t="s">
         <v>1283</v>
       </c>
@@ -15898,6 +18017,9 @@
       <c r="B233" s="1">
         <v>14</v>
       </c>
+      <c r="C233" t="s">
+        <v>2644</v>
+      </c>
       <c r="D233" s="1" t="s">
         <v>1283</v>
       </c>
@@ -15933,6 +18055,9 @@
       <c r="B234" s="1">
         <v>14</v>
       </c>
+      <c r="C234" t="s">
+        <v>2645</v>
+      </c>
       <c r="D234" s="1" t="s">
         <v>1288</v>
       </c>
@@ -15968,6 +18093,9 @@
       <c r="B235" s="1">
         <v>14</v>
       </c>
+      <c r="C235" t="s">
+        <v>2646</v>
+      </c>
       <c r="D235" s="1" t="s">
         <v>1288</v>
       </c>
@@ -16003,6 +18131,9 @@
       <c r="B236" s="1">
         <v>14</v>
       </c>
+      <c r="C236" t="s">
+        <v>2647</v>
+      </c>
       <c r="D236" s="1" t="s">
         <v>1288</v>
       </c>
@@ -16038,6 +18169,9 @@
       <c r="B237" s="1">
         <v>14</v>
       </c>
+      <c r="C237" t="s">
+        <v>2648</v>
+      </c>
       <c r="D237" s="1" t="s">
         <v>1294</v>
       </c>
@@ -16073,6 +18207,9 @@
       <c r="B238" s="1">
         <v>14</v>
       </c>
+      <c r="C238" t="s">
+        <v>2649</v>
+      </c>
       <c r="D238" s="1" t="s">
         <v>1297</v>
       </c>
@@ -16108,6 +18245,9 @@
       <c r="B239" s="1">
         <v>14</v>
       </c>
+      <c r="C239" t="s">
+        <v>2650</v>
+      </c>
       <c r="D239" s="1" t="s">
         <v>1301</v>
       </c>
@@ -16143,6 +18283,9 @@
       <c r="B240" s="1">
         <v>14</v>
       </c>
+      <c r="C240" t="s">
+        <v>2651</v>
+      </c>
       <c r="D240" s="1" t="s">
         <v>1305</v>
       </c>
@@ -16178,6 +18321,9 @@
       <c r="B241" s="1">
         <v>14</v>
       </c>
+      <c r="C241" t="s">
+        <v>2652</v>
+      </c>
       <c r="D241" s="1" t="s">
         <v>1308</v>
       </c>
@@ -16213,6 +18359,9 @@
       <c r="B242" s="1">
         <v>14</v>
       </c>
+      <c r="C242" t="s">
+        <v>2653</v>
+      </c>
       <c r="D242" s="1" t="s">
         <v>1301</v>
       </c>
@@ -16248,6 +18397,9 @@
       <c r="B243" s="1">
         <v>14</v>
       </c>
+      <c r="C243" t="s">
+        <v>2654</v>
+      </c>
       <c r="D243" s="1" t="s">
         <v>1313</v>
       </c>
@@ -16283,6 +18435,9 @@
       <c r="B244" s="1">
         <v>14</v>
       </c>
+      <c r="C244" t="s">
+        <v>2655</v>
+      </c>
       <c r="D244" s="1" t="s">
         <v>1320</v>
       </c>
@@ -16318,6 +18473,9 @@
       <c r="B245" s="1">
         <v>14</v>
       </c>
+      <c r="C245" t="s">
+        <v>2656</v>
+      </c>
       <c r="D245" s="1" t="s">
         <v>1324</v>
       </c>
@@ -16353,6 +18511,9 @@
       <c r="B246" s="1">
         <v>14</v>
       </c>
+      <c r="C246" t="s">
+        <v>2657</v>
+      </c>
       <c r="D246" s="1" t="s">
         <v>1301</v>
       </c>
@@ -16388,6 +18549,9 @@
       <c r="B247" s="1">
         <v>15</v>
       </c>
+      <c r="C247" t="s">
+        <v>2658</v>
+      </c>
       <c r="D247" s="1" t="s">
         <v>1331</v>
       </c>
@@ -16423,6 +18587,9 @@
       <c r="B248" s="1">
         <v>15</v>
       </c>
+      <c r="C248" t="s">
+        <v>2659</v>
+      </c>
       <c r="D248" s="1" t="s">
         <v>1335</v>
       </c>
@@ -16458,6 +18625,9 @@
       <c r="B249" s="1">
         <v>15</v>
       </c>
+      <c r="C249" t="s">
+        <v>2660</v>
+      </c>
       <c r="D249" s="1" t="s">
         <v>1335</v>
       </c>
@@ -16493,6 +18663,9 @@
       <c r="B250" s="1">
         <v>15</v>
       </c>
+      <c r="C250" t="s">
+        <v>2661</v>
+      </c>
       <c r="D250" s="1" t="s">
         <v>1340</v>
       </c>
@@ -16528,6 +18701,9 @@
       <c r="B251" s="1">
         <v>15</v>
       </c>
+      <c r="C251" t="s">
+        <v>2662</v>
+      </c>
       <c r="D251" s="1" t="s">
         <v>1344</v>
       </c>
@@ -16563,6 +18739,9 @@
       <c r="B252" s="1">
         <v>15</v>
       </c>
+      <c r="C252" t="s">
+        <v>2663</v>
+      </c>
       <c r="D252" s="1" t="s">
         <v>1347</v>
       </c>
@@ -16598,6 +18777,9 @@
       <c r="B253" s="1">
         <v>16</v>
       </c>
+      <c r="C253" t="s">
+        <v>2664</v>
+      </c>
       <c r="D253" s="1" t="s">
         <v>1350</v>
       </c>
@@ -16633,6 +18815,9 @@
       <c r="B254" s="1">
         <v>16</v>
       </c>
+      <c r="C254" t="s">
+        <v>2665</v>
+      </c>
       <c r="D254" s="1" t="s">
         <v>1350</v>
       </c>
@@ -16668,6 +18853,9 @@
       <c r="B255" s="1">
         <v>16</v>
       </c>
+      <c r="C255" t="s">
+        <v>2666</v>
+      </c>
       <c r="D255" s="1" t="s">
         <v>1357</v>
       </c>
@@ -16703,6 +18891,9 @@
       <c r="B256" s="1">
         <v>16</v>
       </c>
+      <c r="C256" t="s">
+        <v>2667</v>
+      </c>
       <c r="D256" s="1" t="s">
         <v>1360</v>
       </c>
@@ -16738,6 +18929,9 @@
       <c r="B257" s="1">
         <v>16</v>
       </c>
+      <c r="C257" t="s">
+        <v>2668</v>
+      </c>
       <c r="D257" s="1" t="s">
         <v>1364</v>
       </c>
@@ -16773,6 +18967,9 @@
       <c r="B258" s="1">
         <v>16</v>
       </c>
+      <c r="C258" t="s">
+        <v>2669</v>
+      </c>
       <c r="D258" s="1" t="s">
         <v>1371</v>
       </c>
@@ -16808,6 +19005,9 @@
       <c r="B259" s="1">
         <v>16</v>
       </c>
+      <c r="C259" t="s">
+        <v>2670</v>
+      </c>
       <c r="D259" s="1" t="s">
         <v>1374</v>
       </c>
@@ -16843,6 +19043,9 @@
       <c r="B260" s="1">
         <v>16</v>
       </c>
+      <c r="C260" t="s">
+        <v>2671</v>
+      </c>
       <c r="D260" s="1" t="s">
         <v>1378</v>
       </c>
@@ -16878,6 +19081,9 @@
       <c r="B261" s="1">
         <v>17</v>
       </c>
+      <c r="C261" t="s">
+        <v>2678</v>
+      </c>
       <c r="D261" s="1" t="s">
         <v>1381</v>
       </c>
@@ -16913,6 +19119,9 @@
       <c r="B262" s="1">
         <v>17</v>
       </c>
+      <c r="C262" t="s">
+        <v>2679</v>
+      </c>
       <c r="D262" s="1" t="s">
         <v>1388</v>
       </c>
@@ -16948,6 +19157,9 @@
       <c r="B263" s="1">
         <v>17</v>
       </c>
+      <c r="C263" t="s">
+        <v>2680</v>
+      </c>
       <c r="D263" s="1" t="s">
         <v>1395</v>
       </c>
@@ -16983,6 +19195,9 @@
       <c r="B264" s="1">
         <v>17</v>
       </c>
+      <c r="C264" t="s">
+        <v>2681</v>
+      </c>
       <c r="D264" s="1" t="s">
         <v>1400</v>
       </c>
@@ -17018,6 +19233,9 @@
       <c r="B265" s="1">
         <v>18</v>
       </c>
+      <c r="C265" t="s">
+        <v>2682</v>
+      </c>
       <c r="D265" s="1" t="s">
         <v>1405</v>
       </c>
@@ -17053,6 +19271,9 @@
       <c r="B266" s="1">
         <v>18</v>
       </c>
+      <c r="C266" t="s">
+        <v>2683</v>
+      </c>
       <c r="D266" s="1" t="s">
         <v>1405</v>
       </c>
@@ -17088,6 +19309,9 @@
       <c r="B267" s="1">
         <v>18</v>
       </c>
+      <c r="C267" t="s">
+        <v>2684</v>
+      </c>
       <c r="D267" s="1" t="s">
         <v>1405</v>
       </c>
@@ -17123,6 +19347,9 @@
       <c r="B268" s="1">
         <v>19</v>
       </c>
+      <c r="C268" t="s">
+        <v>2672</v>
+      </c>
       <c r="D268" s="1" t="s">
         <v>1414</v>
       </c>
@@ -17158,6 +19385,9 @@
       <c r="B269" s="1">
         <v>19</v>
       </c>
+      <c r="C269" t="s">
+        <v>2673</v>
+      </c>
       <c r="D269" s="1" t="s">
         <v>1414</v>
       </c>
@@ -17193,6 +19423,9 @@
       <c r="B270" s="1">
         <v>20</v>
       </c>
+      <c r="C270" t="s">
+        <v>2674</v>
+      </c>
       <c r="D270" s="1" t="s">
         <v>1422</v>
       </c>
@@ -17228,6 +19461,9 @@
       <c r="B271" s="1">
         <v>21</v>
       </c>
+      <c r="C271" t="s">
+        <v>2675</v>
+      </c>
       <c r="D271" s="1" t="s">
         <v>1429</v>
       </c>
@@ -17263,6 +19499,9 @@
       <c r="B272" s="1">
         <v>21</v>
       </c>
+      <c r="C272" t="s">
+        <v>2676</v>
+      </c>
       <c r="D272" s="1" t="s">
         <v>1429</v>
       </c>
@@ -17298,6 +19537,9 @@
       <c r="B273" s="1">
         <v>22</v>
       </c>
+      <c r="C273" t="s">
+        <v>2677</v>
+      </c>
       <c r="D273" s="1" t="s">
         <v>1436</v>
       </c>
@@ -17333,6 +19575,9 @@
       <c r="B274" s="1">
         <v>22</v>
       </c>
+      <c r="C274" t="s">
+        <v>2685</v>
+      </c>
       <c r="D274" s="1" t="s">
         <v>1443</v>
       </c>
@@ -17368,6 +19613,9 @@
       <c r="B275" s="1">
         <v>22</v>
       </c>
+      <c r="C275" t="s">
+        <v>2686</v>
+      </c>
       <c r="D275" s="1" t="s">
         <v>1446</v>
       </c>
@@ -17403,6 +19651,9 @@
       <c r="B276" s="1">
         <v>23</v>
       </c>
+      <c r="C276" t="s">
+        <v>2687</v>
+      </c>
       <c r="D276" s="1" t="s">
         <v>1450</v>
       </c>
@@ -17438,6 +19689,9 @@
       <c r="B277" s="1">
         <v>23</v>
       </c>
+      <c r="C277" t="s">
+        <v>2688</v>
+      </c>
       <c r="D277" s="1" t="s">
         <v>1455</v>
       </c>
@@ -17473,6 +19727,9 @@
       <c r="B278" s="1">
         <v>23</v>
       </c>
+      <c r="C278" t="s">
+        <v>2689</v>
+      </c>
       <c r="D278" s="1" t="s">
         <v>1459</v>
       </c>
@@ -17508,6 +19765,9 @@
       <c r="B279" s="1">
         <v>23</v>
       </c>
+      <c r="C279" t="s">
+        <v>2690</v>
+      </c>
       <c r="D279" s="1" t="s">
         <v>1463</v>
       </c>
@@ -17543,6 +19803,9 @@
       <c r="B280" s="1">
         <v>23</v>
       </c>
+      <c r="C280" t="s">
+        <v>2691</v>
+      </c>
       <c r="D280" s="1" t="s">
         <v>1467</v>
       </c>
@@ -17578,6 +19841,9 @@
       <c r="B281" s="1">
         <v>24</v>
       </c>
+      <c r="C281" t="s">
+        <v>2692</v>
+      </c>
       <c r="D281" s="1" t="s">
         <v>1470</v>
       </c>
@@ -17613,6 +19879,9 @@
       <c r="B282" s="1">
         <v>24</v>
       </c>
+      <c r="C282" t="s">
+        <v>2693</v>
+      </c>
       <c r="D282" s="1" t="s">
         <v>1470</v>
       </c>
@@ -17648,6 +19917,9 @@
       <c r="B283" s="1">
         <v>24</v>
       </c>
+      <c r="C283" t="s">
+        <v>2694</v>
+      </c>
       <c r="D283" s="1" t="s">
         <v>1475</v>
       </c>
@@ -17683,6 +19955,9 @@
       <c r="B284" s="1">
         <v>24</v>
       </c>
+      <c r="C284" t="s">
+        <v>2695</v>
+      </c>
       <c r="D284" s="1" t="s">
         <v>1475</v>
       </c>
@@ -17718,6 +19993,9 @@
       <c r="B285" s="1">
         <v>24</v>
       </c>
+      <c r="C285" t="s">
+        <v>2696</v>
+      </c>
       <c r="D285" s="1" t="s">
         <v>1480</v>
       </c>
@@ -17753,6 +20031,9 @@
       <c r="B286" s="1">
         <v>24</v>
       </c>
+      <c r="C286" t="s">
+        <v>2697</v>
+      </c>
       <c r="D286" s="1" t="s">
         <v>1483</v>
       </c>
@@ -17788,6 +20069,9 @@
       <c r="B287" s="1">
         <v>24</v>
       </c>
+      <c r="C287" t="s">
+        <v>2698</v>
+      </c>
       <c r="D287" s="1" t="s">
         <v>1483</v>
       </c>
@@ -17823,6 +20107,9 @@
       <c r="B288" s="1">
         <v>24</v>
       </c>
+      <c r="C288" t="s">
+        <v>2699</v>
+      </c>
       <c r="D288" s="1" t="s">
         <v>1489</v>
       </c>
@@ -17858,6 +20145,9 @@
       <c r="B289" s="1">
         <v>24</v>
       </c>
+      <c r="C289" t="s">
+        <v>2700</v>
+      </c>
       <c r="D289" s="1" t="s">
         <v>1492</v>
       </c>
@@ -17893,6 +20183,9 @@
       <c r="B290" s="1">
         <v>24</v>
       </c>
+      <c r="C290" t="s">
+        <v>2701</v>
+      </c>
       <c r="D290" s="1" t="s">
         <v>1495</v>
       </c>
@@ -17928,6 +20221,9 @@
       <c r="B291" s="1">
         <v>24</v>
       </c>
+      <c r="C291" t="s">
+        <v>2702</v>
+      </c>
       <c r="D291" s="1" t="s">
         <v>1499</v>
       </c>
@@ -17963,6 +20259,9 @@
       <c r="B292" s="1">
         <v>24</v>
       </c>
+      <c r="C292" t="s">
+        <v>2703</v>
+      </c>
       <c r="D292" s="1" t="s">
         <v>1499</v>
       </c>
@@ -17998,6 +20297,9 @@
       <c r="B293" s="1">
         <v>24</v>
       </c>
+      <c r="C293" t="s">
+        <v>2704</v>
+      </c>
       <c r="D293" s="1" t="s">
         <v>1503</v>
       </c>
@@ -18033,6 +20335,9 @@
       <c r="B294" s="1">
         <v>24</v>
       </c>
+      <c r="C294" t="s">
+        <v>2705</v>
+      </c>
       <c r="D294" s="1" t="s">
         <v>1506</v>
       </c>
@@ -18068,6 +20373,9 @@
       <c r="B295" s="1">
         <v>24</v>
       </c>
+      <c r="C295" t="s">
+        <v>2706</v>
+      </c>
       <c r="D295" s="1" t="s">
         <v>1513</v>
       </c>
@@ -18103,6 +20411,9 @@
       <c r="B296" s="1">
         <v>24</v>
       </c>
+      <c r="C296" t="s">
+        <v>2707</v>
+      </c>
       <c r="D296" s="1" t="s">
         <v>1520</v>
       </c>
@@ -18138,6 +20449,9 @@
       <c r="B297" s="1">
         <v>24</v>
       </c>
+      <c r="C297" t="s">
+        <v>2708</v>
+      </c>
       <c r="D297" s="1" t="s">
         <v>1524</v>
       </c>
@@ -18173,6 +20487,9 @@
       <c r="B298" s="1">
         <v>24</v>
       </c>
+      <c r="C298" t="s">
+        <v>2709</v>
+      </c>
       <c r="D298" s="1" t="s">
         <v>1527</v>
       </c>
@@ -18208,6 +20525,9 @@
       <c r="B299" s="1">
         <v>24</v>
       </c>
+      <c r="C299" t="s">
+        <v>2710</v>
+      </c>
       <c r="D299" s="1" t="s">
         <v>1531</v>
       </c>
@@ -18243,6 +20563,9 @@
       <c r="B300" s="1">
         <v>24</v>
       </c>
+      <c r="C300" t="s">
+        <v>2711</v>
+      </c>
       <c r="D300" s="1" t="s">
         <v>1538</v>
       </c>
@@ -18278,6 +20601,9 @@
       <c r="B301" s="1">
         <v>25</v>
       </c>
+      <c r="C301" t="s">
+        <v>2712</v>
+      </c>
       <c r="D301" s="1" t="s">
         <v>1545</v>
       </c>
@@ -18313,6 +20639,9 @@
       <c r="B302" s="1">
         <v>25</v>
       </c>
+      <c r="C302" t="s">
+        <v>2713</v>
+      </c>
       <c r="D302" s="1" t="s">
         <v>1552</v>
       </c>
@@ -18348,6 +20677,9 @@
       <c r="B303" s="1">
         <v>25</v>
       </c>
+      <c r="C303" t="s">
+        <v>2714</v>
+      </c>
       <c r="D303" s="1" t="s">
         <v>1556</v>
       </c>
@@ -18383,6 +20715,9 @@
       <c r="B304" s="1">
         <v>25</v>
       </c>
+      <c r="C304" t="s">
+        <v>2715</v>
+      </c>
       <c r="D304" s="1" t="s">
         <v>1562</v>
       </c>
@@ -18418,6 +20753,9 @@
       <c r="B305" s="1">
         <v>25</v>
       </c>
+      <c r="C305" t="s">
+        <v>2716</v>
+      </c>
       <c r="D305" s="1" t="s">
         <v>1569</v>
       </c>
@@ -18453,6 +20791,9 @@
       <c r="B306" s="1">
         <v>26</v>
       </c>
+      <c r="C306" t="s">
+        <v>2717</v>
+      </c>
       <c r="D306" s="1" t="s">
         <v>1576</v>
       </c>
@@ -18488,6 +20829,9 @@
       <c r="B307" s="1">
         <v>26</v>
       </c>
+      <c r="C307" t="s">
+        <v>2718</v>
+      </c>
       <c r="D307" s="1" t="s">
         <v>1583</v>
       </c>
@@ -18523,6 +20867,9 @@
       <c r="B308" s="1">
         <v>27</v>
       </c>
+      <c r="C308" t="s">
+        <v>2719</v>
+      </c>
       <c r="D308" s="1" t="s">
         <v>1587</v>
       </c>
@@ -18558,6 +20905,9 @@
       <c r="B309" s="1">
         <v>27</v>
       </c>
+      <c r="C309" t="s">
+        <v>2720</v>
+      </c>
       <c r="D309" s="1" t="s">
         <v>1594</v>
       </c>
@@ -18593,6 +20943,9 @@
       <c r="B310" s="1">
         <v>28</v>
       </c>
+      <c r="C310" t="s">
+        <v>2721</v>
+      </c>
       <c r="D310" s="1" t="s">
         <v>1597</v>
       </c>
@@ -18628,6 +20981,9 @@
       <c r="B311" s="1">
         <v>28</v>
       </c>
+      <c r="C311" t="s">
+        <v>2722</v>
+      </c>
       <c r="D311" s="1" t="s">
         <v>1604</v>
       </c>
@@ -18663,6 +21019,9 @@
       <c r="B312" s="1">
         <v>28</v>
       </c>
+      <c r="C312" t="s">
+        <v>2723</v>
+      </c>
       <c r="D312" s="1" t="s">
         <v>1607</v>
       </c>
@@ -18698,6 +21057,9 @@
       <c r="B313" s="1">
         <v>28</v>
       </c>
+      <c r="C313" t="s">
+        <v>2724</v>
+      </c>
       <c r="D313" s="1" t="s">
         <v>1610</v>
       </c>
@@ -18733,6 +21095,9 @@
       <c r="B314" s="1">
         <v>28</v>
       </c>
+      <c r="C314" t="s">
+        <v>2725</v>
+      </c>
       <c r="D314" s="1" t="s">
         <v>1613</v>
       </c>
@@ -18768,6 +21133,9 @@
       <c r="B315" s="1">
         <v>28</v>
       </c>
+      <c r="C315" t="s">
+        <v>2726</v>
+      </c>
       <c r="D315" s="1" t="s">
         <v>1616</v>
       </c>
@@ -18803,6 +21171,9 @@
       <c r="B316" s="1">
         <v>28</v>
       </c>
+      <c r="C316" t="s">
+        <v>2727</v>
+      </c>
       <c r="D316" s="1" t="s">
         <v>1619</v>
       </c>
@@ -18838,6 +21209,9 @@
       <c r="B317" s="1">
         <v>29</v>
       </c>
+      <c r="C317" t="s">
+        <v>2728</v>
+      </c>
       <c r="D317" s="1" t="s">
         <v>1622</v>
       </c>
@@ -18873,6 +21247,9 @@
       <c r="B318" s="1">
         <v>29</v>
       </c>
+      <c r="C318" t="s">
+        <v>2729</v>
+      </c>
       <c r="D318" s="1" t="s">
         <v>1628</v>
       </c>
@@ -18908,6 +21285,9 @@
       <c r="B319" s="1">
         <v>29</v>
       </c>
+      <c r="C319" t="s">
+        <v>2730</v>
+      </c>
       <c r="D319" s="1" t="s">
         <v>1630</v>
       </c>
@@ -18943,6 +21323,9 @@
       <c r="B320" s="1">
         <v>29</v>
       </c>
+      <c r="C320" t="s">
+        <v>2731</v>
+      </c>
       <c r="D320" s="1" t="s">
         <v>1635</v>
       </c>
@@ -18978,6 +21361,9 @@
       <c r="B321" s="1">
         <v>29</v>
       </c>
+      <c r="C321" t="s">
+        <v>2732</v>
+      </c>
       <c r="D321" s="1" t="s">
         <v>1640</v>
       </c>
@@ -19013,6 +21399,9 @@
       <c r="B322" s="1">
         <v>29</v>
       </c>
+      <c r="C322" t="s">
+        <v>2733</v>
+      </c>
       <c r="D322" s="1" t="s">
         <v>1644</v>
       </c>
@@ -19048,6 +21437,9 @@
       <c r="B323" s="1">
         <v>29</v>
       </c>
+      <c r="C323" t="s">
+        <v>2734</v>
+      </c>
       <c r="D323" s="1" t="s">
         <v>1647</v>
       </c>
@@ -19083,6 +21475,9 @@
       <c r="B324" s="1">
         <v>29</v>
       </c>
+      <c r="C324" t="s">
+        <v>2735</v>
+      </c>
       <c r="D324" s="1" t="s">
         <v>1650</v>
       </c>
@@ -19118,6 +21513,9 @@
       <c r="B325" s="1">
         <v>29</v>
       </c>
+      <c r="C325" t="s">
+        <v>2736</v>
+      </c>
       <c r="D325" s="1" t="s">
         <v>1654</v>
       </c>
@@ -19153,6 +21551,9 @@
       <c r="B326" s="1">
         <v>30</v>
       </c>
+      <c r="C326" t="s">
+        <v>2737</v>
+      </c>
       <c r="D326" s="1" t="s">
         <v>1658</v>
       </c>
@@ -19188,6 +21589,9 @@
       <c r="B327" s="1">
         <v>30</v>
       </c>
+      <c r="C327" t="s">
+        <v>2738</v>
+      </c>
       <c r="D327" s="1" t="s">
         <v>1662</v>
       </c>
@@ -19223,6 +21627,9 @@
       <c r="B328" s="1">
         <v>31</v>
       </c>
+      <c r="C328" t="s">
+        <v>2739</v>
+      </c>
       <c r="D328" s="1" t="s">
         <v>1666</v>
       </c>
@@ -19258,6 +21665,9 @@
       <c r="B329" s="1">
         <v>31</v>
       </c>
+      <c r="C329" t="s">
+        <v>2740</v>
+      </c>
       <c r="D329" s="1" t="s">
         <v>1671</v>
       </c>
@@ -19293,6 +21703,9 @@
       <c r="B330" s="1">
         <v>31</v>
       </c>
+      <c r="C330" t="s">
+        <v>2741</v>
+      </c>
       <c r="D330" s="1" t="s">
         <v>1673</v>
       </c>
@@ -19328,6 +21741,9 @@
       <c r="B331" s="1">
         <v>31</v>
       </c>
+      <c r="C331" t="s">
+        <v>2742</v>
+      </c>
       <c r="D331" s="1" t="s">
         <v>1677</v>
       </c>
@@ -19363,6 +21779,9 @@
       <c r="B332" s="1">
         <v>31</v>
       </c>
+      <c r="C332" t="s">
+        <v>2743</v>
+      </c>
       <c r="D332" s="1" t="s">
         <v>1680</v>
       </c>
@@ -19398,6 +21817,9 @@
       <c r="B333" s="1">
         <v>31</v>
       </c>
+      <c r="C333" t="s">
+        <v>2744</v>
+      </c>
       <c r="D333" s="1" t="s">
         <v>1687</v>
       </c>
@@ -19433,6 +21855,9 @@
       <c r="B334" s="1">
         <v>32</v>
       </c>
+      <c r="C334" t="s">
+        <v>2745</v>
+      </c>
       <c r="D334" s="1" t="s">
         <v>1694</v>
       </c>
@@ -19468,6 +21893,9 @@
       <c r="B335" s="1">
         <v>32</v>
       </c>
+      <c r="C335" t="s">
+        <v>2746</v>
+      </c>
       <c r="D335" s="1" t="s">
         <v>1698</v>
       </c>
@@ -19503,6 +21931,9 @@
       <c r="B336" s="1">
         <v>32</v>
       </c>
+      <c r="C336" t="s">
+        <v>2747</v>
+      </c>
       <c r="D336" s="1" t="s">
         <v>1705</v>
       </c>
@@ -19538,6 +21969,9 @@
       <c r="B337" s="1">
         <v>32</v>
       </c>
+      <c r="C337" t="s">
+        <v>2748</v>
+      </c>
       <c r="D337" s="1" t="s">
         <v>1709</v>
       </c>
@@ -19573,6 +22007,9 @@
       <c r="B338" s="1">
         <v>33</v>
       </c>
+      <c r="C338" t="s">
+        <v>2749</v>
+      </c>
       <c r="D338" s="1" t="s">
         <v>1713</v>
       </c>
@@ -19608,6 +22045,9 @@
       <c r="B339" s="1">
         <v>33</v>
       </c>
+      <c r="C339" t="s">
+        <v>2750</v>
+      </c>
       <c r="D339" s="1" t="s">
         <v>1717</v>
       </c>
@@ -19643,6 +22083,9 @@
       <c r="B340" s="1">
         <v>34</v>
       </c>
+      <c r="C340" t="s">
+        <v>2751</v>
+      </c>
       <c r="D340" s="1" t="s">
         <v>1721</v>
       </c>
@@ -19678,6 +22121,9 @@
       <c r="B341" s="1">
         <v>34</v>
       </c>
+      <c r="C341" t="s">
+        <v>2752</v>
+      </c>
       <c r="D341" s="1" t="s">
         <v>1728</v>
       </c>
@@ -19713,6 +22159,9 @@
       <c r="B342" s="1">
         <v>34</v>
       </c>
+      <c r="C342" t="s">
+        <v>2753</v>
+      </c>
       <c r="D342" s="1" t="s">
         <v>1732</v>
       </c>
@@ -19748,6 +22197,9 @@
       <c r="B343" s="1">
         <v>35</v>
       </c>
+      <c r="C343" t="s">
+        <v>2754</v>
+      </c>
       <c r="D343" s="1" t="s">
         <v>1736</v>
       </c>
@@ -19783,6 +22235,9 @@
       <c r="B344" s="1">
         <v>36</v>
       </c>
+      <c r="C344" t="s">
+        <v>2755</v>
+      </c>
       <c r="D344" s="1" t="s">
         <v>1743</v>
       </c>
@@ -19818,6 +22273,9 @@
       <c r="B345" s="1">
         <v>36</v>
       </c>
+      <c r="C345" t="s">
+        <v>2756</v>
+      </c>
       <c r="D345" s="1" t="s">
         <v>1748</v>
       </c>
@@ -19853,6 +22311,9 @@
       <c r="B346" s="1">
         <v>36</v>
       </c>
+      <c r="C346" t="s">
+        <v>2757</v>
+      </c>
       <c r="D346" s="1" t="s">
         <v>1752</v>
       </c>
@@ -19888,6 +22349,9 @@
       <c r="B347" s="1">
         <v>37</v>
       </c>
+      <c r="C347" t="s">
+        <v>2758</v>
+      </c>
       <c r="D347" s="1" t="s">
         <v>1756</v>
       </c>
@@ -19923,6 +22387,9 @@
       <c r="B348" s="1">
         <v>37</v>
       </c>
+      <c r="C348" t="s">
+        <v>2758</v>
+      </c>
       <c r="D348" s="1" t="s">
         <v>1761</v>
       </c>
@@ -19958,6 +22425,9 @@
       <c r="B349" s="1">
         <v>38</v>
       </c>
+      <c r="C349" t="s">
+        <v>2759</v>
+      </c>
       <c r="D349" s="1" t="s">
         <v>1765</v>
       </c>
@@ -19993,6 +22463,9 @@
       <c r="B350" s="1">
         <v>38</v>
       </c>
+      <c r="C350" t="s">
+        <v>2760</v>
+      </c>
       <c r="D350" s="1" t="s">
         <v>1770</v>
       </c>
@@ -20028,6 +22501,9 @@
       <c r="B351" s="1">
         <v>38</v>
       </c>
+      <c r="C351" t="s">
+        <v>2761</v>
+      </c>
       <c r="D351" s="1" t="s">
         <v>1774</v>
       </c>
@@ -20063,6 +22539,9 @@
       <c r="B352" s="1">
         <v>38</v>
       </c>
+      <c r="C352" t="s">
+        <v>2762</v>
+      </c>
       <c r="D352" s="1" t="s">
         <v>1777</v>
       </c>
@@ -20098,6 +22577,9 @@
       <c r="B353" s="1">
         <v>38</v>
       </c>
+      <c r="C353" t="s">
+        <v>2763</v>
+      </c>
       <c r="D353" s="1" t="s">
         <v>1781</v>
       </c>
@@ -20133,6 +22615,9 @@
       <c r="B354" s="1">
         <v>38</v>
       </c>
+      <c r="C354" t="s">
+        <v>2764</v>
+      </c>
       <c r="D354" s="1" t="s">
         <v>1786</v>
       </c>
@@ -20168,6 +22653,9 @@
       <c r="B355" s="1">
         <v>38</v>
       </c>
+      <c r="C355" t="s">
+        <v>2765</v>
+      </c>
       <c r="D355" s="1" t="s">
         <v>1789</v>
       </c>
@@ -20203,6 +22691,9 @@
       <c r="B356" s="1">
         <v>39</v>
       </c>
+      <c r="C356" t="s">
+        <v>2766</v>
+      </c>
       <c r="D356" s="1" t="s">
         <v>1795</v>
       </c>
@@ -20238,6 +22729,9 @@
       <c r="B357" s="1">
         <v>39</v>
       </c>
+      <c r="C357" t="s">
+        <v>2767</v>
+      </c>
       <c r="D357" s="1" t="s">
         <v>1802</v>
       </c>
@@ -20273,6 +22767,9 @@
       <c r="B358" s="1">
         <v>39</v>
       </c>
+      <c r="C358" t="s">
+        <v>2766</v>
+      </c>
       <c r="D358" s="1" t="s">
         <v>1806</v>
       </c>
@@ -20308,6 +22805,9 @@
       <c r="B359" s="1">
         <v>39</v>
       </c>
+      <c r="C359" t="s">
+        <v>2766</v>
+      </c>
       <c r="D359" s="1" t="s">
         <v>1811</v>
       </c>
@@ -20343,6 +22843,9 @@
       <c r="B360" s="1">
         <v>40</v>
       </c>
+      <c r="C360" t="s">
+        <v>2768</v>
+      </c>
       <c r="D360" s="1" t="s">
         <v>1815</v>
       </c>
@@ -20378,6 +22881,9 @@
       <c r="B361" s="1">
         <v>40</v>
       </c>
+      <c r="C361" t="s">
+        <v>2769</v>
+      </c>
       <c r="D361" s="1" t="s">
         <v>1822</v>
       </c>
@@ -20413,6 +22919,9 @@
       <c r="B362" s="1">
         <v>40</v>
       </c>
+      <c r="C362" t="s">
+        <v>2770</v>
+      </c>
       <c r="D362" s="1" t="s">
         <v>1826</v>
       </c>
@@ -20448,6 +22957,9 @@
       <c r="B363" s="1">
         <v>40</v>
       </c>
+      <c r="C363" t="s">
+        <v>2771</v>
+      </c>
       <c r="D363" s="1" t="s">
         <v>1829</v>
       </c>
@@ -20483,6 +22995,9 @@
       <c r="B364" s="1">
         <v>40</v>
       </c>
+      <c r="C364" t="s">
+        <v>2772</v>
+      </c>
       <c r="D364" s="1" t="s">
         <v>1833</v>
       </c>
@@ -20518,6 +23033,9 @@
       <c r="B365" s="1">
         <v>40</v>
       </c>
+      <c r="C365" t="s">
+        <v>2773</v>
+      </c>
       <c r="D365" s="1" t="s">
         <v>1836</v>
       </c>
@@ -20553,6 +23071,9 @@
       <c r="B366" s="1">
         <v>41</v>
       </c>
+      <c r="C366" t="s">
+        <v>2774</v>
+      </c>
       <c r="D366" s="1" t="s">
         <v>1840</v>
       </c>
@@ -20588,6 +23109,9 @@
       <c r="B367" s="1">
         <v>41</v>
       </c>
+      <c r="C367" t="s">
+        <v>2775</v>
+      </c>
       <c r="D367" s="1" t="s">
         <v>1847</v>
       </c>
@@ -20623,6 +23147,9 @@
       <c r="B368" s="1">
         <v>41</v>
       </c>
+      <c r="C368" t="s">
+        <v>2776</v>
+      </c>
       <c r="D368" s="1" t="s">
         <v>1851</v>
       </c>
@@ -20658,6 +23185,9 @@
       <c r="B369" s="1">
         <v>42</v>
       </c>
+      <c r="C369" t="s">
+        <v>2777</v>
+      </c>
       <c r="D369" s="1" t="s">
         <v>1855</v>
       </c>
@@ -20693,6 +23223,9 @@
       <c r="B370" s="1">
         <v>42</v>
       </c>
+      <c r="C370" t="s">
+        <v>2778</v>
+      </c>
       <c r="D370" s="1" t="s">
         <v>1862</v>
       </c>
@@ -20728,6 +23261,9 @@
       <c r="B371" s="1">
         <v>42</v>
       </c>
+      <c r="C371" t="s">
+        <v>2779</v>
+      </c>
       <c r="D371" s="1" t="s">
         <v>1866</v>
       </c>
@@ -20763,6 +23299,9 @@
       <c r="B372" s="1">
         <v>42</v>
       </c>
+      <c r="C372" t="s">
+        <v>2780</v>
+      </c>
       <c r="D372" s="1" t="s">
         <v>1869</v>
       </c>
@@ -20798,6 +23337,9 @@
       <c r="B373" s="1">
         <v>43</v>
       </c>
+      <c r="C373" t="s">
+        <v>2781</v>
+      </c>
       <c r="D373" s="1" t="s">
         <v>1872</v>
       </c>
@@ -20833,6 +23375,9 @@
       <c r="B374" s="1">
         <v>43</v>
       </c>
+      <c r="C374" t="s">
+        <v>2782</v>
+      </c>
       <c r="D374" s="1" t="s">
         <v>1879</v>
       </c>
@@ -20868,6 +23413,9 @@
       <c r="B375" s="1">
         <v>43</v>
       </c>
+      <c r="C375" t="s">
+        <v>2783</v>
+      </c>
       <c r="D375" s="1" t="s">
         <v>1882</v>
       </c>
@@ -20903,6 +23451,9 @@
       <c r="B376" s="1">
         <v>43</v>
       </c>
+      <c r="C376" t="s">
+        <v>2784</v>
+      </c>
       <c r="D376" s="1" t="s">
         <v>1882</v>
       </c>
@@ -20938,6 +23489,9 @@
       <c r="B377" s="1">
         <v>44</v>
       </c>
+      <c r="C377" t="s">
+        <v>2785</v>
+      </c>
       <c r="D377" s="1" t="s">
         <v>1886</v>
       </c>
@@ -20973,6 +23527,9 @@
       <c r="B378" s="1">
         <v>44</v>
       </c>
+      <c r="C378" t="s">
+        <v>2786</v>
+      </c>
       <c r="D378" s="1" t="s">
         <v>1891</v>
       </c>
@@ -21008,6 +23565,9 @@
       <c r="B379" s="1">
         <v>44</v>
       </c>
+      <c r="C379" t="s">
+        <v>2787</v>
+      </c>
       <c r="D379" s="1" t="s">
         <v>1896</v>
       </c>
@@ -21043,6 +23603,9 @@
       <c r="B380" s="1">
         <v>44</v>
       </c>
+      <c r="C380" t="s">
+        <v>2788</v>
+      </c>
       <c r="D380" s="1" t="s">
         <v>1901</v>
       </c>
@@ -21078,6 +23641,9 @@
       <c r="B381" s="1">
         <v>44</v>
       </c>
+      <c r="C381" t="s">
+        <v>2789</v>
+      </c>
       <c r="D381" s="1" t="s">
         <v>1908</v>
       </c>
@@ -21113,6 +23679,9 @@
       <c r="B382" s="1">
         <v>44</v>
       </c>
+      <c r="C382" t="s">
+        <v>2790</v>
+      </c>
       <c r="D382" s="1" t="s">
         <v>1915</v>
       </c>
@@ -21148,6 +23717,9 @@
       <c r="B383" s="1">
         <v>44</v>
       </c>
+      <c r="C383" t="s">
+        <v>2791</v>
+      </c>
       <c r="D383" s="1" t="s">
         <v>1921</v>
       </c>
@@ -21183,6 +23755,9 @@
       <c r="B384" s="1">
         <v>44</v>
       </c>
+      <c r="C384" t="s">
+        <v>2792</v>
+      </c>
       <c r="D384" s="1" t="s">
         <v>1927</v>
       </c>
@@ -21218,6 +23793,9 @@
       <c r="B385" s="1">
         <v>44</v>
       </c>
+      <c r="C385" t="s">
+        <v>2793</v>
+      </c>
       <c r="D385" s="1" t="s">
         <v>1935</v>
       </c>
@@ -21253,6 +23831,9 @@
       <c r="B386" s="1">
         <v>44</v>
       </c>
+      <c r="C386" t="s">
+        <v>2794</v>
+      </c>
       <c r="D386" s="1" t="s">
         <v>1938</v>
       </c>
@@ -21288,6 +23869,9 @@
       <c r="B387" s="1">
         <v>44</v>
       </c>
+      <c r="C387" t="s">
+        <v>2795</v>
+      </c>
       <c r="D387" s="1" t="s">
         <v>1945</v>
       </c>
@@ -21323,6 +23907,9 @@
       <c r="B388" s="1">
         <v>44</v>
       </c>
+      <c r="C388" t="s">
+        <v>2796</v>
+      </c>
       <c r="D388" s="1" t="s">
         <v>1952</v>
       </c>
@@ -21358,6 +23945,9 @@
       <c r="B389" s="1">
         <v>44</v>
       </c>
+      <c r="C389" t="s">
+        <v>2797</v>
+      </c>
       <c r="D389" s="1" t="s">
         <v>1958</v>
       </c>
@@ -21393,6 +23983,9 @@
       <c r="B390" s="1">
         <v>44</v>
       </c>
+      <c r="C390" t="s">
+        <v>2798</v>
+      </c>
       <c r="D390" s="1" t="s">
         <v>1963</v>
       </c>
@@ -21428,6 +24021,9 @@
       <c r="B391" s="1">
         <v>44</v>
       </c>
+      <c r="C391" t="s">
+        <v>2799</v>
+      </c>
       <c r="D391" s="1" t="s">
         <v>1967</v>
       </c>
@@ -21463,6 +24059,9 @@
       <c r="B392" s="1">
         <v>44</v>
       </c>
+      <c r="C392" t="s">
+        <v>2800</v>
+      </c>
       <c r="D392" s="1" t="s">
         <v>1974</v>
       </c>
@@ -21498,6 +24097,9 @@
       <c r="B393" s="1">
         <v>44</v>
       </c>
+      <c r="C393" t="s">
+        <v>2801</v>
+      </c>
       <c r="D393" s="1" t="s">
         <v>1981</v>
       </c>
@@ -21533,6 +24135,9 @@
       <c r="B394" s="1">
         <v>44</v>
       </c>
+      <c r="C394" t="s">
+        <v>2802</v>
+      </c>
       <c r="D394" s="1" t="s">
         <v>1985</v>
       </c>
@@ -21568,6 +24173,9 @@
       <c r="B395" s="1">
         <v>44</v>
       </c>
+      <c r="C395" t="s">
+        <v>2803</v>
+      </c>
       <c r="D395" s="1" t="s">
         <v>1987</v>
       </c>
@@ -21603,6 +24211,9 @@
       <c r="B396" s="1">
         <v>44</v>
       </c>
+      <c r="C396" t="s">
+        <v>2804</v>
+      </c>
       <c r="D396" s="1" t="s">
         <v>1991</v>
       </c>
@@ -21638,6 +24249,9 @@
       <c r="B397" s="1">
         <v>44</v>
       </c>
+      <c r="C397" t="s">
+        <v>2805</v>
+      </c>
       <c r="D397" s="1" t="s">
         <v>1993</v>
       </c>
@@ -21673,6 +24287,9 @@
       <c r="B398" s="1">
         <v>44</v>
       </c>
+      <c r="C398" t="s">
+        <v>2806</v>
+      </c>
       <c r="D398" s="1" t="s">
         <v>1997</v>
       </c>
@@ -21708,6 +24325,9 @@
       <c r="B399" s="1">
         <v>44</v>
       </c>
+      <c r="C399" t="s">
+        <v>2807</v>
+      </c>
       <c r="D399" s="1" t="s">
         <v>2001</v>
       </c>
@@ -21743,6 +24363,9 @@
       <c r="B400" s="1">
         <v>44</v>
       </c>
+      <c r="C400" t="s">
+        <v>2808</v>
+      </c>
       <c r="D400" s="1" t="s">
         <v>2005</v>
       </c>
@@ -21778,6 +24401,9 @@
       <c r="B401" s="1">
         <v>44</v>
       </c>
+      <c r="C401" t="s">
+        <v>2809</v>
+      </c>
       <c r="D401" s="1" t="s">
         <v>2007</v>
       </c>
@@ -21813,6 +24439,9 @@
       <c r="B402" s="1">
         <v>44</v>
       </c>
+      <c r="C402" t="s">
+        <v>2810</v>
+      </c>
       <c r="D402" s="1" t="s">
         <v>2009</v>
       </c>
@@ -21848,6 +24477,9 @@
       <c r="B403" s="1">
         <v>44</v>
       </c>
+      <c r="C403" t="s">
+        <v>2785</v>
+      </c>
       <c r="D403" s="1" t="s">
         <v>2013</v>
       </c>
@@ -21883,6 +24515,9 @@
       <c r="B404" s="1">
         <v>45</v>
       </c>
+      <c r="C404" t="s">
+        <v>2811</v>
+      </c>
       <c r="D404" s="1" t="s">
         <v>2020</v>
       </c>
@@ -21918,6 +24553,9 @@
       <c r="B405" s="1">
         <v>45</v>
       </c>
+      <c r="C405" t="s">
+        <v>2811</v>
+      </c>
       <c r="D405" s="1" t="s">
         <v>2026</v>
       </c>
@@ -21953,6 +24591,9 @@
       <c r="B406" s="1">
         <v>46</v>
       </c>
+      <c r="C406" t="s">
+        <v>2812</v>
+      </c>
       <c r="D406" s="1" t="s">
         <v>2033</v>
       </c>
@@ -21988,6 +24629,9 @@
       <c r="B407" s="1">
         <v>46</v>
       </c>
+      <c r="C407" t="s">
+        <v>2813</v>
+      </c>
       <c r="D407" s="1" t="s">
         <v>2039</v>
       </c>
@@ -22023,6 +24667,9 @@
       <c r="B408" s="1">
         <v>46</v>
       </c>
+      <c r="C408" t="s">
+        <v>2814</v>
+      </c>
       <c r="D408" s="1" t="s">
         <v>2043</v>
       </c>
@@ -22058,6 +24705,9 @@
       <c r="B409" s="1">
         <v>46</v>
       </c>
+      <c r="C409" t="s">
+        <v>2815</v>
+      </c>
       <c r="D409" s="1" t="s">
         <v>2047</v>
       </c>
@@ -22093,6 +24743,9 @@
       <c r="B410" s="1">
         <v>46</v>
       </c>
+      <c r="C410" t="s">
+        <v>2816</v>
+      </c>
       <c r="D410" s="1" t="s">
         <v>2054</v>
       </c>
@@ -22128,6 +24781,9 @@
       <c r="B411" s="1">
         <v>46</v>
       </c>
+      <c r="C411" t="s">
+        <v>2817</v>
+      </c>
       <c r="D411" s="1" t="s">
         <v>2061</v>
       </c>
@@ -22163,6 +24819,9 @@
       <c r="B412" s="1">
         <v>47</v>
       </c>
+      <c r="C412" t="s">
+        <v>2818</v>
+      </c>
       <c r="D412" s="1" t="s">
         <v>2064</v>
       </c>
@@ -22198,6 +24857,9 @@
       <c r="B413" s="1">
         <v>47</v>
       </c>
+      <c r="C413" t="s">
+        <v>2819</v>
+      </c>
       <c r="D413" s="1" t="s">
         <v>2071</v>
       </c>
@@ -22233,6 +24895,9 @@
       <c r="B414" s="1">
         <v>47</v>
       </c>
+      <c r="C414" t="s">
+        <v>2820</v>
+      </c>
       <c r="D414" s="1" t="s">
         <v>2074</v>
       </c>
@@ -22268,6 +24933,9 @@
       <c r="B415" s="1">
         <v>47</v>
       </c>
+      <c r="C415" t="s">
+        <v>2821</v>
+      </c>
       <c r="D415" s="1" t="s">
         <v>2078</v>
       </c>
@@ -22303,6 +24971,9 @@
       <c r="B416" s="1">
         <v>47</v>
       </c>
+      <c r="C416" t="s">
+        <v>2822</v>
+      </c>
       <c r="D416" s="1" t="s">
         <v>2082</v>
       </c>
@@ -22338,6 +25009,9 @@
       <c r="B417" s="1">
         <v>48</v>
       </c>
+      <c r="C417" t="s">
+        <v>2823</v>
+      </c>
       <c r="D417" s="1" t="s">
         <v>2085</v>
       </c>
@@ -22373,6 +25047,9 @@
       <c r="B418" s="1">
         <v>48</v>
       </c>
+      <c r="C418" t="s">
+        <v>2824</v>
+      </c>
       <c r="D418" s="1" t="s">
         <v>2085</v>
       </c>
@@ -22408,6 +25085,9 @@
       <c r="B419" s="1">
         <v>49</v>
       </c>
+      <c r="C419" t="s">
+        <v>2825</v>
+      </c>
       <c r="D419" s="1" t="s">
         <v>2090</v>
       </c>
@@ -22443,6 +25123,9 @@
       <c r="B420" s="1">
         <v>49</v>
       </c>
+      <c r="C420" t="s">
+        <v>2826</v>
+      </c>
       <c r="D420" s="1" t="s">
         <v>2097</v>
       </c>
@@ -22478,6 +25161,9 @@
       <c r="B421" s="1">
         <v>49</v>
       </c>
+      <c r="C421" t="s">
+        <v>2827</v>
+      </c>
       <c r="D421" s="1" t="s">
         <v>2100</v>
       </c>
@@ -22513,6 +25199,9 @@
       <c r="B422" s="1">
         <v>49</v>
       </c>
+      <c r="C422" t="s">
+        <v>2828</v>
+      </c>
       <c r="D422" s="1" t="s">
         <v>2104</v>
       </c>
@@ -22548,6 +25237,9 @@
       <c r="B423" s="1">
         <v>49</v>
       </c>
+      <c r="C423" t="s">
+        <v>2829</v>
+      </c>
       <c r="D423" s="1" t="s">
         <v>2110</v>
       </c>
@@ -22583,6 +25275,9 @@
       <c r="B424" s="1">
         <v>50</v>
       </c>
+      <c r="C424" t="s">
+        <v>2830</v>
+      </c>
       <c r="D424" s="1" t="s">
         <v>2115</v>
       </c>
@@ -22618,6 +25313,9 @@
       <c r="B425" s="1">
         <v>50</v>
       </c>
+      <c r="C425" t="s">
+        <v>2831</v>
+      </c>
       <c r="D425" s="1" t="s">
         <v>2122</v>
       </c>
@@ -22653,6 +25351,9 @@
       <c r="B426" s="1">
         <v>50</v>
       </c>
+      <c r="C426" t="s">
+        <v>2833</v>
+      </c>
       <c r="D426" s="1" t="s">
         <v>2126</v>
       </c>
@@ -22688,6 +25389,9 @@
       <c r="B427" s="1">
         <v>50</v>
       </c>
+      <c r="C427" t="s">
+        <v>2832</v>
+      </c>
       <c r="D427" s="1" t="s">
         <v>2130</v>
       </c>
@@ -22723,6 +25427,9 @@
       <c r="B428" s="1">
         <v>51</v>
       </c>
+      <c r="C428" t="s">
+        <v>2834</v>
+      </c>
       <c r="D428" s="1" t="s">
         <v>2134</v>
       </c>
@@ -22758,6 +25465,9 @@
       <c r="B429" s="1">
         <v>51</v>
       </c>
+      <c r="C429" t="s">
+        <v>2835</v>
+      </c>
       <c r="D429" s="1" t="s">
         <v>2141</v>
       </c>
@@ -22793,6 +25503,9 @@
       <c r="B430" s="1">
         <v>51</v>
       </c>
+      <c r="C430" t="s">
+        <v>2836</v>
+      </c>
       <c r="D430" s="1" t="s">
         <v>2144</v>
       </c>
@@ -22828,6 +25541,9 @@
       <c r="B431" s="1">
         <v>52</v>
       </c>
+      <c r="C431" t="s">
+        <v>2837</v>
+      </c>
       <c r="D431" s="1" t="s">
         <v>2147</v>
       </c>
@@ -22863,6 +25579,9 @@
       <c r="B432" s="1">
         <v>52</v>
       </c>
+      <c r="C432" t="s">
+        <v>2838</v>
+      </c>
       <c r="D432" s="1" t="s">
         <v>2154</v>
       </c>
@@ -22898,6 +25617,9 @@
       <c r="B433" s="1">
         <v>52</v>
       </c>
+      <c r="C433" t="s">
+        <v>2839</v>
+      </c>
       <c r="D433" s="1" t="s">
         <v>2154</v>
       </c>
@@ -22933,6 +25655,9 @@
       <c r="B434" s="1">
         <v>53</v>
       </c>
+      <c r="C434" t="s">
+        <v>2840</v>
+      </c>
       <c r="D434" s="1" t="s">
         <v>2159</v>
       </c>
@@ -22968,6 +25693,9 @@
       <c r="B435" s="1">
         <v>53</v>
       </c>
+      <c r="C435" t="s">
+        <v>2841</v>
+      </c>
       <c r="D435" s="1" t="s">
         <v>2163</v>
       </c>
@@ -23003,6 +25731,9 @@
       <c r="B436" s="1">
         <v>53</v>
       </c>
+      <c r="C436" t="s">
+        <v>2842</v>
+      </c>
       <c r="D436" s="1" t="s">
         <v>2167</v>
       </c>
@@ -23038,6 +25769,9 @@
       <c r="B437" s="1">
         <v>53</v>
       </c>
+      <c r="C437" t="s">
+        <v>2843</v>
+      </c>
       <c r="D437" s="1" t="s">
         <v>2170</v>
       </c>
@@ -23073,6 +25807,9 @@
       <c r="B438" s="1">
         <v>54</v>
       </c>
+      <c r="C438" t="s">
+        <v>2844</v>
+      </c>
       <c r="D438" s="1" t="s">
         <v>2174</v>
       </c>
@@ -23108,6 +25845,9 @@
       <c r="B439" s="1">
         <v>54</v>
       </c>
+      <c r="C439" t="s">
+        <v>2845</v>
+      </c>
       <c r="D439" s="1" t="s">
         <v>2178</v>
       </c>
@@ -23143,6 +25883,9 @@
       <c r="B440" s="1">
         <v>54</v>
       </c>
+      <c r="C440" t="s">
+        <v>2846</v>
+      </c>
       <c r="D440" s="1" t="s">
         <v>2182</v>
       </c>
@@ -23178,6 +25921,9 @@
       <c r="B441" s="1">
         <v>55</v>
       </c>
+      <c r="C441" t="s">
+        <v>2847</v>
+      </c>
       <c r="D441" s="1" t="s">
         <v>2186</v>
       </c>
@@ -23213,6 +25959,9 @@
       <c r="B442" s="1">
         <v>55</v>
       </c>
+      <c r="C442" t="s">
+        <v>2848</v>
+      </c>
       <c r="D442" s="1" t="s">
         <v>2190</v>
       </c>
@@ -23248,6 +25997,9 @@
       <c r="B443" s="1">
         <v>56</v>
       </c>
+      <c r="C443" t="s">
+        <v>2849</v>
+      </c>
       <c r="D443" s="1" t="s">
         <v>2194</v>
       </c>
@@ -23283,6 +26035,9 @@
       <c r="B444" s="1">
         <v>56</v>
       </c>
+      <c r="C444" t="s">
+        <v>2849</v>
+      </c>
       <c r="D444" s="1" t="s">
         <v>2201</v>
       </c>
@@ -23318,6 +26073,9 @@
       <c r="B445" s="1">
         <v>57</v>
       </c>
+      <c r="C445" t="s">
+        <v>2850</v>
+      </c>
       <c r="D445" s="1" t="s">
         <v>2205</v>
       </c>
@@ -23353,6 +26111,9 @@
       <c r="B446" s="1">
         <v>57</v>
       </c>
+      <c r="C446" t="s">
+        <v>2851</v>
+      </c>
       <c r="D446" s="1" t="s">
         <v>2212</v>
       </c>
@@ -23388,6 +26149,9 @@
       <c r="B447" s="1">
         <v>57</v>
       </c>
+      <c r="C447" t="s">
+        <v>2852</v>
+      </c>
       <c r="D447" s="1" t="s">
         <v>2215</v>
       </c>
@@ -23423,6 +26187,9 @@
       <c r="B448" s="1">
         <v>58</v>
       </c>
+      <c r="C448" t="s">
+        <v>2853</v>
+      </c>
       <c r="D448" s="1" t="s">
         <v>2219</v>
       </c>
@@ -23458,6 +26225,9 @@
       <c r="B449" s="1">
         <v>58</v>
       </c>
+      <c r="C449" t="s">
+        <v>2854</v>
+      </c>
       <c r="D449" s="1" t="s">
         <v>2226</v>
       </c>
@@ -23493,6 +26263,9 @@
       <c r="B450" s="1">
         <v>59</v>
       </c>
+      <c r="C450" t="s">
+        <v>2855</v>
+      </c>
       <c r="D450" s="1" t="s">
         <v>2230</v>
       </c>
@@ -23528,6 +26301,9 @@
       <c r="B451" s="1">
         <v>59</v>
       </c>
+      <c r="C451" t="s">
+        <v>2856</v>
+      </c>
       <c r="D451" s="1" t="s">
         <v>2237</v>
       </c>
@@ -23563,6 +26339,9 @@
       <c r="B452" s="1">
         <v>59</v>
       </c>
+      <c r="C452" t="s">
+        <v>2857</v>
+      </c>
       <c r="D452" s="1" t="s">
         <v>2241</v>
       </c>
@@ -23598,6 +26377,9 @@
       <c r="B453" s="1">
         <v>60</v>
       </c>
+      <c r="C453" t="s">
+        <v>2858</v>
+      </c>
       <c r="D453" s="1" t="s">
         <v>2246</v>
       </c>
@@ -23633,6 +26415,9 @@
       <c r="B454" s="1">
         <v>61</v>
       </c>
+      <c r="C454" t="s">
+        <v>2859</v>
+      </c>
       <c r="D454" s="1" t="s">
         <v>2253</v>
       </c>
@@ -23668,6 +26453,9 @@
       <c r="B455" s="1">
         <v>61</v>
       </c>
+      <c r="C455" t="s">
+        <v>2860</v>
+      </c>
       <c r="D455" s="1" t="s">
         <v>2260</v>
       </c>
@@ -23703,6 +26491,9 @@
       <c r="B456" s="1">
         <v>61</v>
       </c>
+      <c r="C456" t="s">
+        <v>2861</v>
+      </c>
       <c r="D456" s="1" t="s">
         <v>2260</v>
       </c>
@@ -23738,6 +26529,9 @@
       <c r="B457" s="1">
         <v>61</v>
       </c>
+      <c r="C457" t="s">
+        <v>2862</v>
+      </c>
       <c r="D457" s="1" t="s">
         <v>2271</v>
       </c>
@@ -23773,6 +26567,9 @@
       <c r="B458" s="1">
         <v>61</v>
       </c>
+      <c r="C458" t="s">
+        <v>2863</v>
+      </c>
       <c r="D458" s="1" t="s">
         <v>2277</v>
       </c>
@@ -23808,6 +26605,9 @@
       <c r="B459" s="1">
         <v>61</v>
       </c>
+      <c r="C459" t="s">
+        <v>2864</v>
+      </c>
       <c r="D459" s="1" t="s">
         <v>2283</v>
       </c>
@@ -23843,6 +26643,9 @@
       <c r="B460" s="1">
         <v>61</v>
       </c>
+      <c r="C460" t="s">
+        <v>2865</v>
+      </c>
       <c r="D460" s="1" t="s">
         <v>2290</v>
       </c>
@@ -23878,6 +26681,9 @@
       <c r="B461" s="1">
         <v>61</v>
       </c>
+      <c r="C461" t="s">
+        <v>2866</v>
+      </c>
       <c r="D461" s="1" t="s">
         <v>2296</v>
       </c>
@@ -23913,6 +26719,9 @@
       <c r="B462" s="1">
         <v>61</v>
       </c>
+      <c r="C462" t="s">
+        <v>2867</v>
+      </c>
       <c r="D462" s="1" t="s">
         <v>2300</v>
       </c>
@@ -23948,6 +26757,9 @@
       <c r="B463" s="1">
         <v>61</v>
       </c>
+      <c r="C463" t="s">
+        <v>2868</v>
+      </c>
       <c r="D463" s="1" t="s">
         <v>2306</v>
       </c>
@@ -23983,6 +26795,9 @@
       <c r="B464" s="1">
         <v>61</v>
       </c>
+      <c r="C464" t="s">
+        <v>2869</v>
+      </c>
       <c r="D464" s="1" t="s">
         <v>2310</v>
       </c>
@@ -24018,6 +26833,9 @@
       <c r="B465" s="1">
         <v>61</v>
       </c>
+      <c r="C465" t="s">
+        <v>2870</v>
+      </c>
       <c r="D465" s="1" t="s">
         <v>2316</v>
       </c>
@@ -24053,6 +26871,9 @@
       <c r="B466" s="1">
         <v>61</v>
       </c>
+      <c r="C466" t="s">
+        <v>2871</v>
+      </c>
       <c r="D466" s="1" t="s">
         <v>2323</v>
       </c>
@@ -24088,6 +26909,9 @@
       <c r="B467" s="1">
         <v>61</v>
       </c>
+      <c r="C467" t="s">
+        <v>2872</v>
+      </c>
       <c r="D467" s="1" t="s">
         <v>2330</v>
       </c>
@@ -24123,6 +26947,9 @@
       <c r="B468" s="1">
         <v>61</v>
       </c>
+      <c r="C468" t="s">
+        <v>2873</v>
+      </c>
       <c r="D468" s="1" t="s">
         <v>2334</v>
       </c>
@@ -24158,6 +26985,9 @@
       <c r="B469" s="1">
         <v>61</v>
       </c>
+      <c r="C469" t="s">
+        <v>2874</v>
+      </c>
       <c r="D469" s="1" t="s">
         <v>2341</v>
       </c>
@@ -24193,6 +27023,9 @@
       <c r="B470" s="1">
         <v>62</v>
       </c>
+      <c r="C470" t="s">
+        <v>2875</v>
+      </c>
       <c r="D470" s="1" t="s">
         <v>2348</v>
       </c>
@@ -24228,6 +27061,9 @@
       <c r="B471" s="1">
         <v>63</v>
       </c>
+      <c r="C471" t="s">
+        <v>2876</v>
+      </c>
       <c r="D471" s="1" t="s">
         <v>2355</v>
       </c>
@@ -24263,6 +27099,9 @@
       <c r="B472" s="1">
         <v>63</v>
       </c>
+      <c r="C472" t="s">
+        <v>2878</v>
+      </c>
       <c r="D472" s="1" t="s">
         <v>2359</v>
       </c>
@@ -24298,6 +27137,9 @@
       <c r="B473" s="1">
         <v>63</v>
       </c>
+      <c r="C473" t="s">
+        <v>2879</v>
+      </c>
       <c r="D473" s="1" t="s">
         <v>2364</v>
       </c>
@@ -24333,6 +27175,9 @@
       <c r="B474" s="1">
         <v>63</v>
       </c>
+      <c r="C474" t="s">
+        <v>2880</v>
+      </c>
       <c r="D474" s="1" t="s">
         <v>2367</v>
       </c>
@@ -24368,6 +27213,9 @@
       <c r="B475" s="1">
         <v>63</v>
       </c>
+      <c r="C475" t="s">
+        <v>2881</v>
+      </c>
       <c r="D475" s="1" t="s">
         <v>2372</v>
       </c>
@@ -24403,6 +27251,9 @@
       <c r="B476" s="1">
         <v>63</v>
       </c>
+      <c r="C476" t="s">
+        <v>2882</v>
+      </c>
       <c r="D476" s="1" t="s">
         <v>2377</v>
       </c>
@@ -24438,6 +27289,9 @@
       <c r="B477" s="1">
         <v>64</v>
       </c>
+      <c r="C477" t="s">
+        <v>2877</v>
+      </c>
       <c r="D477" s="1" t="s">
         <v>2380</v>
       </c>
@@ -24473,6 +27327,9 @@
       <c r="B478" s="1">
         <v>64</v>
       </c>
+      <c r="C478" t="s">
+        <v>2883</v>
+      </c>
       <c r="D478" s="1" t="s">
         <v>2384</v>
       </c>
@@ -24508,6 +27365,9 @@
       <c r="B479" s="1">
         <v>64</v>
       </c>
+      <c r="C479" t="s">
+        <v>2884</v>
+      </c>
       <c r="D479" s="1" t="s">
         <v>2388</v>
       </c>
@@ -24543,6 +27403,9 @@
       <c r="B480" s="1">
         <v>64</v>
       </c>
+      <c r="C480" t="s">
+        <v>2885</v>
+      </c>
       <c r="D480" s="1" t="s">
         <v>2392</v>
       </c>
@@ -24578,6 +27441,9 @@
       <c r="B481" s="1">
         <v>65</v>
       </c>
+      <c r="C481" t="s">
+        <v>2886</v>
+      </c>
       <c r="D481" s="1" t="s">
         <v>2396</v>
       </c>
@@ -24613,6 +27479,9 @@
       <c r="B482" s="1">
         <v>66</v>
       </c>
+      <c r="C482" t="s">
+        <v>2887</v>
+      </c>
       <c r="D482" s="1" t="s">
         <v>2400</v>
       </c>
@@ -24647,6 +27516,9 @@
       </c>
       <c r="B483" s="1">
         <v>66</v>
+      </c>
+      <c r="C483" t="s">
+        <v>2887</v>
       </c>
       <c r="D483" s="1" t="s">
         <v>2407</v>
